--- a/research/traditional_assets/database/data/bulgaria/bulgaria_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_real_estate_development.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_nlc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +589,29 @@
           <t>Real Estate (Development)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.132</v>
+      </c>
+      <c r="E2">
+        <v>-0.05299999999999999</v>
+      </c>
+      <c r="G2">
+        <v>0.8972431077694235</v>
+      </c>
+      <c r="H2">
+        <v>0.8972431077694235</v>
+      </c>
+      <c r="I2">
+        <v>0.1503759398496241</v>
+      </c>
+      <c r="J2">
+        <v>0.1468317257790942</v>
+      </c>
       <c r="K2">
-        <v>0.326</v>
+        <v>0.178</v>
+      </c>
+      <c r="L2">
+        <v>0.4461152882205514</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +635,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.015</v>
+        <v>2.466</v>
       </c>
       <c r="V2">
-        <v>0.001442307692307692</v>
-      </c>
-      <c r="W2">
-        <v>0.03578485181119649</v>
+        <v>0.02401168451801363</v>
       </c>
       <c r="X2">
-        <v>0.08780599874638154</v>
-      </c>
-      <c r="Y2">
-        <v>-0.05202114693518504</v>
+        <v>0.1571901089672386</v>
       </c>
       <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-0.002324974654941587</v>
+        <v>0.008647594278283485</v>
       </c>
       <c r="AB2">
-        <v>0.05784305348742207</v>
-      </c>
-      <c r="AC2">
-        <v>-0.06016802814236365</v>
+        <v>0.09355809632681669</v>
       </c>
       <c r="AD2">
-        <v>17.6</v>
+        <v>39.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17.6</v>
+        <v>39.5</v>
       </c>
       <c r="AG2">
-        <v>17.585</v>
+        <v>37.034</v>
       </c>
       <c r="AH2">
-        <v>0.6285714285714287</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AI2">
-        <v>0.606896551724138</v>
+        <v>0.3973843058350101</v>
       </c>
       <c r="AJ2">
-        <v>0.6283723423262463</v>
+        <v>0.265032132480284</v>
       </c>
       <c r="AK2">
-        <v>0.6066931171295498</v>
+        <v>0.3820537685435451</v>
       </c>
       <c r="AL2">
-        <v>1.25</v>
+        <v>1.518</v>
       </c>
       <c r="AM2">
-        <v>1.204</v>
+        <v>1.446</v>
+      </c>
+      <c r="AN2">
+        <v>589.5522388059702</v>
       </c>
       <c r="AO2">
-        <v>-0.06320000000000001</v>
+        <v>0.03952569169960474</v>
+      </c>
+      <c r="AP2">
+        <v>552.7462686567164</v>
       </c>
       <c r="AQ2">
-        <v>-0.06561461794019934</v>
+        <v>0.04149377593360996</v>
       </c>
     </row>
     <row r="3">
@@ -691,8 +708,26 @@
           <t>Real Estate (Development)</t>
         </is>
       </c>
+      <c r="E3">
+        <v>0.291</v>
+      </c>
+      <c r="G3">
+        <v>1.206666666666667</v>
+      </c>
+      <c r="H3">
+        <v>1.206666666666667</v>
+      </c>
+      <c r="I3">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="J3">
+        <v>0.2159820426487093</v>
+      </c>
       <c r="K3">
-        <v>0.326</v>
+        <v>0.172</v>
+      </c>
+      <c r="L3">
+        <v>0.5733333333333334</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +751,8901 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.015</v>
+        <v>0.116</v>
       </c>
       <c r="V3">
-        <v>0.001442307692307692</v>
+        <v>0.01104761904761905</v>
+      </c>
+      <c r="X3">
+        <v>0.2316157212357679</v>
+      </c>
+      <c r="AB3">
+        <v>0.1043516959549241</v>
+      </c>
+      <c r="AD3">
+        <v>39.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>39.5</v>
+      </c>
+      <c r="AG3">
+        <v>39.384</v>
+      </c>
+      <c r="AH3">
+        <v>0.79</v>
+      </c>
+      <c r="AI3">
+        <v>0.7328385899814471</v>
+      </c>
+      <c r="AJ3">
+        <v>0.7895116670675968</v>
+      </c>
+      <c r="AK3">
+        <v>0.7322623828647925</v>
+      </c>
+      <c r="AL3">
+        <v>1.51</v>
+      </c>
+      <c r="AM3">
+        <v>1.452</v>
+      </c>
+      <c r="AN3">
+        <v>556.3380281690141</v>
+      </c>
+      <c r="AO3">
+        <v>0.04503311258278146</v>
+      </c>
+      <c r="AP3">
+        <v>554.7042253521128</v>
+      </c>
+      <c r="AQ3">
+        <v>0.04683195592286502</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Galata Investment Company AD (BUL:GTH)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.132</v>
+      </c>
+      <c r="E4">
+        <v>-0.397</v>
+      </c>
+      <c r="G4">
+        <v>-0.0404040404040404</v>
+      </c>
+      <c r="H4">
+        <v>-0.0404040404040404</v>
+      </c>
+      <c r="I4">
+        <v>-0.0808080808080808</v>
+      </c>
+      <c r="J4">
+        <v>-0.0808080808080808</v>
+      </c>
+      <c r="K4">
+        <v>0.006</v>
+      </c>
+      <c r="L4">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2.35</v>
+      </c>
+      <c r="V4">
+        <v>0.0254880694143167</v>
+      </c>
+      <c r="W4">
+        <v>0.0001226993865030675</v>
+      </c>
+      <c r="X4">
+        <v>0.08276449669870928</v>
+      </c>
+      <c r="Y4">
+        <v>-0.08264179731220621</v>
+      </c>
+      <c r="Z4">
+        <v>0.002145643693107933</v>
+      </c>
+      <c r="AA4">
+        <v>-0.0001733853489380147</v>
+      </c>
+      <c r="AB4">
+        <v>0.08276449669870928</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08293788204764729</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-2.35</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.02615470228158041</v>
+      </c>
+      <c r="AK4">
+        <v>-0.0544611819235226</v>
+      </c>
+      <c r="AL4">
+        <v>0.008</v>
+      </c>
+      <c r="AM4">
+        <v>-0.006</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-1</v>
+      </c>
+      <c r="AP4">
+        <v>587.5</v>
+      </c>
+      <c r="AQ4">
+        <v>1.333333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Neo London Capital PLC (BUL:NLC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:NLC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.79</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>10.5</v>
+      </c>
+      <c r="H2">
+        <v>74.493760387541</v>
+      </c>
+      <c r="I2">
+        <v>49.884</v>
+      </c>
+      <c r="J2">
+        <v>74.377760387541</v>
+      </c>
+      <c r="K2">
+        <v>39.5</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.104351695954924</v>
+      </c>
+      <c r="N2">
+        <v>0.08276449669870931</v>
+      </c>
+      <c r="O2">
+        <v>0.0705220183486239</v>
+      </c>
+      <c r="P2">
+        <v>0.04113</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.231615721235768</v>
+      </c>
+      <c r="T2">
+        <v>0.08276449669870931</v>
+      </c>
+      <c r="U2">
+        <v>2.22314359473447</v>
+      </c>
+      <c r="V2">
+        <v>0.50690570563978</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>10.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.07835779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>0.004</v>
+      </c>
+      <c r="AI2">
+        <v>-0.003000000000000006</v>
+      </c>
+      <c r="AJ2">
+        <v>39.5</v>
+      </c>
+      <c r="AK2">
+        <v>39.5</v>
+      </c>
+      <c r="AL2">
+        <v>1.51</v>
+      </c>
+      <c r="AM2">
+        <v>39.5</v>
+      </c>
+      <c r="AN2">
+        <v>0.116</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08276449669870928</v>
+      </c>
+      <c r="C2">
+        <v>74.49376038754096</v>
+      </c>
+      <c r="D2">
+        <v>74.37776038754096</v>
+      </c>
+      <c r="E2">
+        <v>-39.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.116</v>
+      </c>
+      <c r="H2">
+        <v>10.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K2">
+        <v>0.004</v>
+      </c>
+      <c r="L2">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.006699999999999998</v>
+      </c>
+      <c r="P2">
+        <v>0.06029999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.0643</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08276449669870928</v>
+      </c>
+      <c r="T2">
+        <v>0.5069057056397804</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W2">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08435294177561468</v>
+      </c>
+      <c r="C3">
+        <v>71.40018502854879</v>
+      </c>
+      <c r="D3">
+        <v>71.78418502854879</v>
+      </c>
+      <c r="E3">
+        <v>-39</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0.116</v>
+      </c>
+      <c r="H3">
+        <v>10.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K3">
+        <v>0.004</v>
+      </c>
+      <c r="L3">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.1069</v>
+      </c>
+      <c r="N3">
+        <v>-0.0399</v>
+      </c>
+      <c r="O3">
+        <v>-0.00399</v>
+      </c>
+      <c r="P3">
+        <v>-0.03591</v>
+      </c>
+      <c r="Q3">
+        <v>-0.03191000000000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08318074926829766</v>
+      </c>
+      <c r="T3">
+        <v>0.5117050509833098</v>
+      </c>
+      <c r="U3">
+        <v>0.2138</v>
+      </c>
+      <c r="V3">
+        <v>0.06267539756782038</v>
       </c>
       <c r="W3">
-        <v>0.03578485181119649</v>
-      </c>
-      <c r="X3">
-        <v>0.08780599874638154</v>
+        <v>0.2004</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.05202114693518504</v>
+        <v>0.6267539756782039</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
-      <c r="AA3">
-        <v>-0.002324974654941587</v>
-      </c>
-      <c r="AB3">
-        <v>0.05784305348742207</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06016802814236365</v>
-      </c>
-      <c r="AD3">
-        <v>17.6</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>17.6</v>
-      </c>
-      <c r="AG3">
-        <v>17.585</v>
-      </c>
-      <c r="AH3">
-        <v>0.6285714285714287</v>
-      </c>
-      <c r="AI3">
-        <v>0.606896551724138</v>
-      </c>
-      <c r="AJ3">
-        <v>0.6283723423262463</v>
-      </c>
-      <c r="AK3">
-        <v>0.6066931171295498</v>
-      </c>
-      <c r="AL3">
-        <v>1.25</v>
-      </c>
-      <c r="AM3">
-        <v>1.204</v>
-      </c>
-      <c r="AO3">
-        <v>-0.06320000000000001</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.06561461794019934</v>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08660582650374435</v>
+      </c>
+      <c r="C4">
+        <v>67.51730252238848</v>
+      </c>
+      <c r="D4">
+        <v>68.40130252238848</v>
+      </c>
+      <c r="E4">
+        <v>-38.5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.116</v>
+      </c>
+      <c r="H4">
+        <v>10.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K4">
+        <v>0.004</v>
+      </c>
+      <c r="L4">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.2388</v>
+      </c>
+      <c r="N4">
+        <v>-0.1718</v>
+      </c>
+      <c r="O4">
+        <v>-0.01718</v>
+      </c>
+      <c r="P4">
+        <v>-0.15462</v>
+      </c>
+      <c r="Q4">
+        <v>-0.15062</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08363655765688199</v>
+      </c>
+      <c r="T4">
+        <v>0.5169604704740703</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>0.02805695142378558</v>
+      </c>
+      <c r="W4">
+        <v>0.2321</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.2805695142378559</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08860582650374434</v>
+      </c>
+      <c r="C5">
+        <v>64.27058362124762</v>
+      </c>
+      <c r="D5">
+        <v>65.65458362124762</v>
+      </c>
+      <c r="E5">
+        <v>-38</v>
+      </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
+      <c r="G5">
+        <v>0.116</v>
+      </c>
+      <c r="H5">
+        <v>10.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K5">
+        <v>0.004</v>
+      </c>
+      <c r="L5">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.3582</v>
+      </c>
+      <c r="N5">
+        <v>-0.2912</v>
+      </c>
+      <c r="O5">
+        <v>-0.02912</v>
+      </c>
+      <c r="P5">
+        <v>-0.26208</v>
+      </c>
+      <c r="Q5">
+        <v>-0.25808</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08409879021004571</v>
+      </c>
+      <c r="T5">
+        <v>0.5222899598604009</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.01870463428252372</v>
+      </c>
+      <c r="W5">
+        <v>0.2343333333333334</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.1870463428252372</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09060582650374434</v>
+      </c>
+      <c r="C6">
+        <v>61.23594271105956</v>
+      </c>
+      <c r="D6">
+        <v>63.11994271105956</v>
+      </c>
+      <c r="E6">
+        <v>-37.5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0.116</v>
+      </c>
+      <c r="H6">
+        <v>10.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K6">
+        <v>0.004</v>
+      </c>
+      <c r="L6">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.4776</v>
+      </c>
+      <c r="N6">
+        <v>-0.4106</v>
+      </c>
+      <c r="O6">
+        <v>-0.04105999999999999</v>
+      </c>
+      <c r="P6">
+        <v>-0.36954</v>
+      </c>
+      <c r="Q6">
+        <v>-0.36554</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08457065260806702</v>
+      </c>
+      <c r="T6">
+        <v>0.5277304802756134</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.01402847571189279</v>
+      </c>
+      <c r="W6">
+        <v>0.23545</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.140284757118928</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09260582650374434</v>
+      </c>
+      <c r="C7">
+        <v>58.38973053247081</v>
+      </c>
+      <c r="D7">
+        <v>60.77373053247081</v>
+      </c>
+      <c r="E7">
+        <v>-37</v>
+      </c>
+      <c r="F7">
+        <v>2.5</v>
+      </c>
+      <c r="G7">
+        <v>0.116</v>
+      </c>
+      <c r="H7">
+        <v>10.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K7">
+        <v>0.004</v>
+      </c>
+      <c r="L7">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.597</v>
+      </c>
+      <c r="N7">
+        <v>-0.53</v>
+      </c>
+      <c r="O7">
+        <v>-0.05299999999999999</v>
+      </c>
+      <c r="P7">
+        <v>-0.477</v>
+      </c>
+      <c r="Q7">
+        <v>-0.473</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08505244895130984</v>
+      </c>
+      <c r="T7">
+        <v>0.5332855379627253</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.01122278056951423</v>
+      </c>
+      <c r="W7">
+        <v>0.23612</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.1122278056951423</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09460582650374433</v>
+      </c>
+      <c r="C8">
+        <v>55.71168804694672</v>
+      </c>
+      <c r="D8">
+        <v>58.59568804694672</v>
+      </c>
+      <c r="E8">
+        <v>-36.5</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0.116</v>
+      </c>
+      <c r="H8">
+        <v>10.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K8">
+        <v>0.004</v>
+      </c>
+      <c r="L8">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.7164</v>
+      </c>
+      <c r="N8">
+        <v>-0.6494000000000001</v>
+      </c>
+      <c r="O8">
+        <v>-0.06494</v>
+      </c>
+      <c r="P8">
+        <v>-0.5844600000000001</v>
+      </c>
+      <c r="Q8">
+        <v>-0.5804600000000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08554449628057909</v>
+      </c>
+      <c r="T8">
+        <v>0.538958788366584</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.009352317141261862</v>
+      </c>
+      <c r="W8">
+        <v>0.2365666666666667</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.09352317141261857</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09660582650374434</v>
+      </c>
+      <c r="C9">
+        <v>53.18435995249757</v>
+      </c>
+      <c r="D9">
+        <v>56.56835995249757</v>
+      </c>
+      <c r="E9">
+        <v>-36</v>
+      </c>
+      <c r="F9">
+        <v>3.5</v>
+      </c>
+      <c r="G9">
+        <v>0.116</v>
+      </c>
+      <c r="H9">
+        <v>10.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K9">
+        <v>0.004</v>
+      </c>
+      <c r="L9">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.8358000000000001</v>
+      </c>
+      <c r="N9">
+        <v>-0.7688000000000001</v>
+      </c>
+      <c r="O9">
+        <v>-0.07688</v>
+      </c>
+      <c r="P9">
+        <v>-0.6919200000000001</v>
+      </c>
+      <c r="Q9">
+        <v>-0.6879200000000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08604712527284339</v>
+      </c>
+      <c r="T9">
+        <v>0.544754044155472</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.00801627183536731</v>
+      </c>
+      <c r="W9">
+        <v>0.2368857142857143</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.08016271835367306</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09860582650374437</v>
+      </c>
+      <c r="C10">
+        <v>50.79262587709083</v>
+      </c>
+      <c r="D10">
+        <v>54.67662587709084</v>
+      </c>
+      <c r="E10">
+        <v>-35.5</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>0.116</v>
+      </c>
+      <c r="H10">
+        <v>10.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K10">
+        <v>0.004</v>
+      </c>
+      <c r="L10">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.9552</v>
+      </c>
+      <c r="N10">
+        <v>-0.8882000000000001</v>
+      </c>
+      <c r="O10">
+        <v>-0.08882</v>
+      </c>
+      <c r="P10">
+        <v>-0.7993800000000001</v>
+      </c>
+      <c r="Q10">
+        <v>-0.7953800000000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08656068098233083</v>
+      </c>
+      <c r="T10">
+        <v>0.5506752837658576</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.007014237855946395</v>
+      </c>
+      <c r="W10">
+        <v>0.237125</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.07014237855946392</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1006058265037444</v>
+      </c>
+      <c r="C11">
+        <v>48.52332259388732</v>
+      </c>
+      <c r="D11">
+        <v>52.90732259388732</v>
+      </c>
+      <c r="E11">
+        <v>-35</v>
+      </c>
+      <c r="F11">
+        <v>4.5</v>
+      </c>
+      <c r="G11">
+        <v>0.116</v>
+      </c>
+      <c r="H11">
+        <v>10.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K11">
+        <v>0.004</v>
+      </c>
+      <c r="L11">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M11">
+        <v>1.0746</v>
+      </c>
+      <c r="N11">
+        <v>-1.0076</v>
+      </c>
+      <c r="O11">
+        <v>-0.10076</v>
+      </c>
+      <c r="P11">
+        <v>-0.9068400000000001</v>
+      </c>
+      <c r="Q11">
+        <v>-0.9028400000000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0870855236304883</v>
+      </c>
+      <c r="T11">
+        <v>0.5567266605105373</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.006234878094174575</v>
+      </c>
+      <c r="W11">
+        <v>0.2373111111111111</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.06234878094174567</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1026058265037444</v>
+      </c>
+      <c r="C12">
+        <v>46.364937286684</v>
+      </c>
+      <c r="D12">
+        <v>51.248937286684</v>
+      </c>
+      <c r="E12">
+        <v>-34.5</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0.116</v>
+      </c>
+      <c r="H12">
+        <v>10.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K12">
+        <v>0.004</v>
+      </c>
+      <c r="L12">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M12">
+        <v>1.194</v>
+      </c>
+      <c r="N12">
+        <v>-1.127</v>
+      </c>
+      <c r="O12">
+        <v>-0.1127</v>
+      </c>
+      <c r="P12">
+        <v>-1.0143</v>
+      </c>
+      <c r="Q12">
+        <v>-1.0103</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08762202944860484</v>
+      </c>
+      <c r="T12">
+        <v>0.5629125122939876</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.005611390284757117</v>
+      </c>
+      <c r="W12">
+        <v>0.23746</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.05611390284757112</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1046058265037444</v>
+      </c>
+      <c r="C13">
+        <v>44.30735674983692</v>
+      </c>
+      <c r="D13">
+        <v>49.69135674983692</v>
+      </c>
+      <c r="E13">
+        <v>-34</v>
+      </c>
+      <c r="F13">
+        <v>5.5</v>
+      </c>
+      <c r="G13">
+        <v>0.116</v>
+      </c>
+      <c r="H13">
+        <v>10.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K13">
+        <v>0.004</v>
+      </c>
+      <c r="L13">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M13">
+        <v>1.3134</v>
+      </c>
+      <c r="N13">
+        <v>-1.2464</v>
+      </c>
+      <c r="O13">
+        <v>-0.12464</v>
+      </c>
+      <c r="P13">
+        <v>-1.12176</v>
+      </c>
+      <c r="Q13">
+        <v>-1.11776</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08817059157724084</v>
+      </c>
+      <c r="T13">
+        <v>0.5692373719826842</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.005101263895233742</v>
+      </c>
+      <c r="W13">
+        <v>0.2375818181818182</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.05101263895233743</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1066058265037443</v>
+      </c>
+      <c r="C14">
+        <v>42.34166097376397</v>
+      </c>
+      <c r="D14">
+        <v>48.22566097376397</v>
+      </c>
+      <c r="E14">
+        <v>-33.5</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>0.116</v>
+      </c>
+      <c r="H14">
+        <v>10.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K14">
+        <v>0.004</v>
+      </c>
+      <c r="L14">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M14">
+        <v>1.4328</v>
+      </c>
+      <c r="N14">
+        <v>-1.3658</v>
+      </c>
+      <c r="O14">
+        <v>-0.13658</v>
+      </c>
+      <c r="P14">
+        <v>-1.22922</v>
+      </c>
+      <c r="Q14">
+        <v>-1.22522</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.0887316210269822</v>
+      </c>
+      <c r="T14">
+        <v>0.5757059784824874</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.004676158570630931</v>
+      </c>
+      <c r="W14">
+        <v>0.2376833333333333</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.04676158570630928</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1086058265037444</v>
+      </c>
+      <c r="C15">
+        <v>40.45995221421859</v>
+      </c>
+      <c r="D15">
+        <v>46.84395221421859</v>
+      </c>
+      <c r="E15">
+        <v>-33</v>
+      </c>
+      <c r="F15">
+        <v>6.5</v>
+      </c>
+      <c r="G15">
+        <v>0.116</v>
+      </c>
+      <c r="H15">
+        <v>10.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K15">
+        <v>0.004</v>
+      </c>
+      <c r="L15">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M15">
+        <v>1.5522</v>
+      </c>
+      <c r="N15">
+        <v>-1.4852</v>
+      </c>
+      <c r="O15">
+        <v>-0.14852</v>
+      </c>
+      <c r="P15">
+        <v>-1.33668</v>
+      </c>
+      <c r="Q15">
+        <v>-1.33268</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08930554770545328</v>
+      </c>
+      <c r="T15">
+        <v>0.5823232885799873</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.004316454065197782</v>
+      </c>
+      <c r="W15">
+        <v>0.2377692307692308</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.04316454065197783</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1106058265037444</v>
+      </c>
+      <c r="C16">
+        <v>38.65521262705498</v>
+      </c>
+      <c r="D16">
+        <v>45.53921262705498</v>
+      </c>
+      <c r="E16">
+        <v>-32.5</v>
+      </c>
+      <c r="F16">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.116</v>
+      </c>
+      <c r="H16">
+        <v>10.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K16">
+        <v>0.004</v>
+      </c>
+      <c r="L16">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M16">
+        <v>1.6716</v>
+      </c>
+      <c r="N16">
+        <v>-1.6046</v>
+      </c>
+      <c r="O16">
+        <v>-0.16046</v>
+      </c>
+      <c r="P16">
+        <v>-1.44414</v>
+      </c>
+      <c r="Q16">
+        <v>-1.44014</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.0898928215159818</v>
+      </c>
+      <c r="T16">
+        <v>0.5890944896099871</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.004008135917683655</v>
+      </c>
+      <c r="W16">
+        <v>0.2378428571428572</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.04008135917683653</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1126058265037443</v>
+      </c>
+      <c r="C17">
+        <v>36.92118504998437</v>
+      </c>
+      <c r="D17">
+        <v>44.30518504998437</v>
+      </c>
+      <c r="E17">
+        <v>-32</v>
+      </c>
+      <c r="F17">
+        <v>7.5</v>
+      </c>
+      <c r="G17">
+        <v>0.116</v>
+      </c>
+      <c r="H17">
+        <v>10.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K17">
+        <v>0.004</v>
+      </c>
+      <c r="L17">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M17">
+        <v>1.791</v>
+      </c>
+      <c r="N17">
+        <v>-1.724</v>
+      </c>
+      <c r="O17">
+        <v>-0.1724</v>
+      </c>
+      <c r="P17">
+        <v>-1.5516</v>
+      </c>
+      <c r="Q17">
+        <v>-1.5476</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09049391353381689</v>
+      </c>
+      <c r="T17">
+        <v>0.5960250130171635</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.003740926856504744</v>
+      </c>
+      <c r="W17">
+        <v>0.2379066666666667</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.03740926856504745</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1146058265037443</v>
+      </c>
+      <c r="C18">
+        <v>35.25227265648132</v>
+      </c>
+      <c r="D18">
+        <v>43.13627265648132</v>
+      </c>
+      <c r="E18">
+        <v>-31.5</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="G18">
+        <v>0.116</v>
+      </c>
+      <c r="H18">
+        <v>10.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K18">
+        <v>0.004</v>
+      </c>
+      <c r="L18">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M18">
+        <v>1.9104</v>
+      </c>
+      <c r="N18">
+        <v>-1.8434</v>
+      </c>
+      <c r="O18">
+        <v>-0.18434</v>
+      </c>
+      <c r="P18">
+        <v>-1.65906</v>
+      </c>
+      <c r="Q18">
+        <v>-1.65506</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09110931726636232</v>
+      </c>
+      <c r="T18">
+        <v>0.6031205488864154</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.003507118927973197</v>
+      </c>
+      <c r="W18">
+        <v>0.2379625</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.03507118927973196</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1166058265037443</v>
+      </c>
+      <c r="C19">
+        <v>33.64345408607759</v>
+      </c>
+      <c r="D19">
+        <v>42.02745408607759</v>
+      </c>
+      <c r="E19">
+        <v>-31</v>
+      </c>
+      <c r="F19">
+        <v>8.5</v>
+      </c>
+      <c r="G19">
+        <v>0.116</v>
+      </c>
+      <c r="H19">
+        <v>10.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K19">
+        <v>0.004</v>
+      </c>
+      <c r="L19">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M19">
+        <v>2.0298</v>
+      </c>
+      <c r="N19">
+        <v>-1.9628</v>
+      </c>
+      <c r="O19">
+        <v>-0.19628</v>
+      </c>
+      <c r="P19">
+        <v>-1.76652</v>
+      </c>
+      <c r="Q19">
+        <v>-1.76252</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09173955000451126</v>
+      </c>
+      <c r="T19">
+        <v>0.6103870615236011</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.00330081781456301</v>
+      </c>
+      <c r="W19">
+        <v>0.2380117647058824</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.03300817814563006</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1186058265037443</v>
+      </c>
+      <c r="C20">
+        <v>32.090211336086</v>
+      </c>
+      <c r="D20">
+        <v>40.974211336086</v>
+      </c>
+      <c r="E20">
+        <v>-30.5</v>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>0.116</v>
+      </c>
+      <c r="H20">
+        <v>10.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K20">
+        <v>0.004</v>
+      </c>
+      <c r="L20">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M20">
+        <v>2.1492</v>
+      </c>
+      <c r="N20">
+        <v>-2.0822</v>
+      </c>
+      <c r="O20">
+        <v>-0.2082199999999999</v>
+      </c>
+      <c r="P20">
+        <v>-1.87398</v>
+      </c>
+      <c r="Q20">
+        <v>-1.86998</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09238515427285895</v>
+      </c>
+      <c r="T20">
+        <v>0.6178308061763279</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.003117439047087287</v>
+      </c>
+      <c r="W20">
+        <v>0.2380555555555556</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.031174390470873</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1206058265037444</v>
+      </c>
+      <c r="C21">
+        <v>30.58846823080216</v>
+      </c>
+      <c r="D21">
+        <v>39.97246823080216</v>
+      </c>
+      <c r="E21">
+        <v>-30</v>
+      </c>
+      <c r="F21">
+        <v>9.5</v>
+      </c>
+      <c r="G21">
+        <v>0.116</v>
+      </c>
+      <c r="H21">
+        <v>10.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K21">
+        <v>0.004</v>
+      </c>
+      <c r="L21">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M21">
+        <v>2.2686</v>
+      </c>
+      <c r="N21">
+        <v>-2.2016</v>
+      </c>
+      <c r="O21">
+        <v>-0.2201599999999999</v>
+      </c>
+      <c r="P21">
+        <v>-1.98144</v>
+      </c>
+      <c r="Q21">
+        <v>-1.97744</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0930466993873387</v>
+      </c>
+      <c r="T21">
+        <v>0.6254583469933197</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.002953363307766904</v>
+      </c>
+      <c r="W21">
+        <v>0.2380947368421053</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.0295336330776691</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1226058265037444</v>
+      </c>
+      <c r="C22">
+        <v>29.13453770118638</v>
+      </c>
+      <c r="D22">
+        <v>39.01853770118638</v>
+      </c>
+      <c r="E22">
+        <v>-29.5</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>0.116</v>
+      </c>
+      <c r="H22">
+        <v>10.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K22">
+        <v>0.004</v>
+      </c>
+      <c r="L22">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M22">
+        <v>2.388</v>
+      </c>
+      <c r="N22">
+        <v>-2.321</v>
+      </c>
+      <c r="O22">
+        <v>-0.2320999999999999</v>
+      </c>
+      <c r="P22">
+        <v>-2.0889</v>
+      </c>
+      <c r="Q22">
+        <v>-2.0849</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09372478312968044</v>
+      </c>
+      <c r="T22">
+        <v>0.6332765763307362</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.002805695142378559</v>
+      </c>
+      <c r="W22">
+        <v>0.23813</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.02805695142378561</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1246058265037444</v>
+      </c>
+      <c r="C23">
+        <v>27.72507643751604</v>
+      </c>
+      <c r="D23">
+        <v>38.10907643751604</v>
+      </c>
+      <c r="E23">
+        <v>-29</v>
+      </c>
+      <c r="F23">
+        <v>10.5</v>
+      </c>
+      <c r="G23">
+        <v>0.116</v>
+      </c>
+      <c r="H23">
+        <v>10.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K23">
+        <v>0.004</v>
+      </c>
+      <c r="L23">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M23">
+        <v>2.5074</v>
+      </c>
+      <c r="N23">
+        <v>-2.4404</v>
+      </c>
+      <c r="O23">
+        <v>-0.2440399999999999</v>
+      </c>
+      <c r="P23">
+        <v>-2.19636</v>
+      </c>
+      <c r="Q23">
+        <v>-2.19236</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09442003354904349</v>
+      </c>
+      <c r="T23">
+        <v>0.6412927355247962</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.002672090611789103</v>
+      </c>
+      <c r="W23">
+        <v>0.2381619047619048</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.02672090611789113</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1266058265037444</v>
+      </c>
+      <c r="C24">
+        <v>26.35704573944179</v>
+      </c>
+      <c r="D24">
+        <v>37.24104573944179</v>
+      </c>
+      <c r="E24">
+        <v>-28.5</v>
+      </c>
+      <c r="F24">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>0.116</v>
+      </c>
+      <c r="H24">
+        <v>10.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K24">
+        <v>0.004</v>
+      </c>
+      <c r="L24">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M24">
+        <v>2.6268</v>
+      </c>
+      <c r="N24">
+        <v>-2.5598</v>
+      </c>
+      <c r="O24">
+        <v>-0.2559799999999999</v>
+      </c>
+      <c r="P24">
+        <v>-2.30382</v>
+      </c>
+      <c r="Q24">
+        <v>-2.29982</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09513311090223635</v>
+      </c>
+      <c r="T24">
+        <v>0.6495144372622935</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.002550631947616871</v>
+      </c>
+      <c r="W24">
+        <v>0.2381909090909091</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.02550631947616877</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1286058265037444</v>
+      </c>
+      <c r="C25">
+        <v>25.02767759732266</v>
+      </c>
+      <c r="D25">
+        <v>36.41167759732266</v>
+      </c>
+      <c r="E25">
+        <v>-28</v>
+      </c>
+      <c r="F25">
+        <v>11.5</v>
+      </c>
+      <c r="G25">
+        <v>0.116</v>
+      </c>
+      <c r="H25">
+        <v>10.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K25">
+        <v>0.004</v>
+      </c>
+      <c r="L25">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M25">
+        <v>2.7462</v>
+      </c>
+      <c r="N25">
+        <v>-2.6792</v>
+      </c>
+      <c r="O25">
+        <v>-0.2679199999999999</v>
+      </c>
+      <c r="P25">
+        <v>-2.41128</v>
+      </c>
+      <c r="Q25">
+        <v>-2.40728</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09586470974512254</v>
+      </c>
+      <c r="T25">
+        <v>0.6579496896942714</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.002439734906416138</v>
+      </c>
+      <c r="W25">
+        <v>0.2382173913043478</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.02439734906416147</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1306058265037444</v>
+      </c>
+      <c r="C26">
+        <v>23.73444520709224</v>
+      </c>
+      <c r="D26">
+        <v>35.61844520709224</v>
+      </c>
+      <c r="E26">
+        <v>-27.5</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>0.116</v>
+      </c>
+      <c r="H26">
+        <v>10.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K26">
+        <v>0.004</v>
+      </c>
+      <c r="L26">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M26">
+        <v>2.8656</v>
+      </c>
+      <c r="N26">
+        <v>-2.7986</v>
+      </c>
+      <c r="O26">
+        <v>-0.2798599999999999</v>
+      </c>
+      <c r="P26">
+        <v>-2.51874</v>
+      </c>
+      <c r="Q26">
+        <v>-2.51474</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09661556118913731</v>
+      </c>
+      <c r="T26">
+        <v>0.6666069224534065</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.002338079285315466</v>
+      </c>
+      <c r="W26">
+        <v>0.2382416666666667</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.02338079285315475</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1326058265037443</v>
+      </c>
+      <c r="C27">
+        <v>22.47503725697582</v>
+      </c>
+      <c r="D27">
+        <v>34.85903725697582</v>
+      </c>
+      <c r="E27">
+        <v>-27</v>
+      </c>
+      <c r="F27">
+        <v>12.5</v>
+      </c>
+      <c r="G27">
+        <v>0.116</v>
+      </c>
+      <c r="H27">
+        <v>10.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K27">
+        <v>0.004</v>
+      </c>
+      <c r="L27">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M27">
+        <v>2.985</v>
+      </c>
+      <c r="N27">
+        <v>-2.918</v>
+      </c>
+      <c r="O27">
+        <v>-0.2917999999999999</v>
+      </c>
+      <c r="P27">
+        <v>-2.6262</v>
+      </c>
+      <c r="Q27">
+        <v>-2.6222</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09738643533832579</v>
+      </c>
+      <c r="T27">
+        <v>0.6754950147527852</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.002244556113902846</v>
+      </c>
+      <c r="W27">
+        <v>0.238264</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.02244556113902851</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1346058265037444</v>
+      </c>
+      <c r="C28">
+        <v>21.24733543488228</v>
+      </c>
+      <c r="D28">
+        <v>34.13133543488228</v>
+      </c>
+      <c r="E28">
+        <v>-26.5</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>0.116</v>
+      </c>
+      <c r="H28">
+        <v>10.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K28">
+        <v>0.004</v>
+      </c>
+      <c r="L28">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M28">
+        <v>3.1044</v>
+      </c>
+      <c r="N28">
+        <v>-3.0374</v>
+      </c>
+      <c r="O28">
+        <v>-0.3037399999999999</v>
+      </c>
+      <c r="P28">
+        <v>-2.73366</v>
+      </c>
+      <c r="Q28">
+        <v>-2.72966</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09817814392397886</v>
+      </c>
+      <c r="T28">
+        <v>0.684623325762958</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.002158227032598891</v>
+      </c>
+      <c r="W28">
+        <v>0.2382846153846154</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.02158227032598903</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1366058265037444</v>
+      </c>
+      <c r="C29">
+        <v>20.04939469546067</v>
+      </c>
+      <c r="D29">
+        <v>33.43339469546067</v>
+      </c>
+      <c r="E29">
+        <v>-26</v>
+      </c>
+      <c r="F29">
+        <v>13.5</v>
+      </c>
+      <c r="G29">
+        <v>0.116</v>
+      </c>
+      <c r="H29">
+        <v>10.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K29">
+        <v>0.004</v>
+      </c>
+      <c r="L29">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M29">
+        <v>3.2238</v>
+      </c>
+      <c r="N29">
+        <v>-3.1568</v>
+      </c>
+      <c r="O29">
+        <v>-0.31568</v>
+      </c>
+      <c r="P29">
+        <v>-2.84112</v>
+      </c>
+      <c r="Q29">
+        <v>-2.83712</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09899154315581418</v>
+      </c>
+      <c r="T29">
+        <v>0.6940017274857383</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.002078292698058191</v>
+      </c>
+      <c r="W29">
+        <v>0.2383037037037037</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.02078292698058193</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1386058265037444</v>
+      </c>
+      <c r="C30">
+        <v>18.87942589971695</v>
+      </c>
+      <c r="D30">
+        <v>32.76342589971695</v>
+      </c>
+      <c r="E30">
+        <v>-25.5</v>
+      </c>
+      <c r="F30">
+        <v>14</v>
+      </c>
+      <c r="G30">
+        <v>0.116</v>
+      </c>
+      <c r="H30">
+        <v>10.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K30">
+        <v>0.004</v>
+      </c>
+      <c r="L30">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M30">
+        <v>3.3432</v>
+      </c>
+      <c r="N30">
+        <v>-3.2762</v>
+      </c>
+      <c r="O30">
+        <v>-0.32762</v>
+      </c>
+      <c r="P30">
+        <v>-2.94858</v>
+      </c>
+      <c r="Q30">
+        <v>-2.94458</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09982753681075605</v>
+      </c>
+      <c r="T30">
+        <v>0.7036406403674847</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.002004067958841828</v>
+      </c>
+      <c r="W30">
+        <v>0.2383214285714286</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.02004067958841838</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1406058265037444</v>
+      </c>
+      <c r="C31">
+        <v>17.73578050092414</v>
+      </c>
+      <c r="D31">
+        <v>32.11978050092414</v>
+      </c>
+      <c r="E31">
+        <v>-25</v>
+      </c>
+      <c r="F31">
+        <v>14.5</v>
+      </c>
+      <c r="G31">
+        <v>0.116</v>
+      </c>
+      <c r="H31">
+        <v>10.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K31">
+        <v>0.004</v>
+      </c>
+      <c r="L31">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M31">
+        <v>3.4626</v>
+      </c>
+      <c r="N31">
+        <v>-3.3956</v>
+      </c>
+      <c r="O31">
+        <v>-0.3395599999999999</v>
+      </c>
+      <c r="P31">
+        <v>-3.056039999999999</v>
+      </c>
+      <c r="Q31">
+        <v>-3.052039999999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1006870795827385</v>
+      </c>
+      <c r="T31">
+        <v>0.7135510719219563</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.001934962167157627</v>
+      </c>
+      <c r="W31">
+        <v>0.2383379310344828</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.01934962167157628</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1426058265037444</v>
+      </c>
+      <c r="C32">
+        <v>16.61693700084824</v>
+      </c>
+      <c r="D32">
+        <v>31.50093700084824</v>
+      </c>
+      <c r="E32">
+        <v>-24.5</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>0.116</v>
+      </c>
+      <c r="H32">
+        <v>10.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K32">
+        <v>0.004</v>
+      </c>
+      <c r="L32">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M32">
+        <v>3.582</v>
+      </c>
+      <c r="N32">
+        <v>-3.515</v>
+      </c>
+      <c r="O32">
+        <v>-0.3514999999999999</v>
+      </c>
+      <c r="P32">
+        <v>-3.1635</v>
+      </c>
+      <c r="Q32">
+        <v>-3.1595</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1015711807196348</v>
+      </c>
+      <c r="T32">
+        <v>0.7237446586636985</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.001870463428252372</v>
+      </c>
+      <c r="W32">
+        <v>0.2383533333333333</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.01870463428252378</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1446058265037443</v>
+      </c>
+      <c r="C33">
+        <v>15.5214889420453</v>
+      </c>
+      <c r="D33">
+        <v>30.9054889420453</v>
+      </c>
+      <c r="E33">
+        <v>-24</v>
+      </c>
+      <c r="F33">
+        <v>15.5</v>
+      </c>
+      <c r="G33">
+        <v>0.116</v>
+      </c>
+      <c r="H33">
+        <v>10.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K33">
+        <v>0.004</v>
+      </c>
+      <c r="L33">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M33">
+        <v>3.7014</v>
+      </c>
+      <c r="N33">
+        <v>-3.6344</v>
+      </c>
+      <c r="O33">
+        <v>-0.3634399999999999</v>
+      </c>
+      <c r="P33">
+        <v>-3.27096</v>
+      </c>
+      <c r="Q33">
+        <v>-3.26696</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1024809079764411</v>
+      </c>
+      <c r="T33">
+        <v>0.73423371168781</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.001810125898308747</v>
+      </c>
+      <c r="W33">
+        <v>0.2383677419354839</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.01810125898308756</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1466058265037443</v>
+      </c>
+      <c r="C34">
+        <v>14.44813423675074</v>
+      </c>
+      <c r="D34">
+        <v>30.33213423675074</v>
+      </c>
+      <c r="E34">
+        <v>-23.5</v>
+      </c>
+      <c r="F34">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>0.116</v>
+      </c>
+      <c r="H34">
+        <v>10.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K34">
+        <v>0.004</v>
+      </c>
+      <c r="L34">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M34">
+        <v>3.8208</v>
+      </c>
+      <c r="N34">
+        <v>-3.7538</v>
+      </c>
+      <c r="O34">
+        <v>-0.3753799999999999</v>
+      </c>
+      <c r="P34">
+        <v>-3.37842</v>
+      </c>
+      <c r="Q34">
+        <v>-3.37442</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1034173919172711</v>
+      </c>
+      <c r="T34">
+        <v>0.7450312662714543</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.001753559463986599</v>
+      </c>
+      <c r="W34">
+        <v>0.23838125</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.01753559463986609</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1486058265037443</v>
+      </c>
+      <c r="C35">
+        <v>13.39566566194853</v>
+      </c>
+      <c r="D35">
+        <v>29.77966566194853</v>
+      </c>
+      <c r="E35">
+        <v>-23</v>
+      </c>
+      <c r="F35">
+        <v>16.5</v>
+      </c>
+      <c r="G35">
+        <v>0.116</v>
+      </c>
+      <c r="H35">
+        <v>10.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K35">
+        <v>0.004</v>
+      </c>
+      <c r="L35">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M35">
+        <v>3.9402</v>
+      </c>
+      <c r="N35">
+        <v>-3.8732</v>
+      </c>
+      <c r="O35">
+        <v>-0.3873199999999999</v>
+      </c>
+      <c r="P35">
+        <v>-3.48588</v>
+      </c>
+      <c r="Q35">
+        <v>-3.48188</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1043818306026035</v>
+      </c>
+      <c r="T35">
+        <v>0.756151135917297</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.001700421298411247</v>
+      </c>
+      <c r="W35">
+        <v>0.2383939393939394</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.01700421298411248</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1506058265037444</v>
+      </c>
+      <c r="C36">
+        <v>12.36296237459434</v>
+      </c>
+      <c r="D36">
+        <v>29.24696237459434</v>
+      </c>
+      <c r="E36">
+        <v>-22.5</v>
+      </c>
+      <c r="F36">
+        <v>17</v>
+      </c>
+      <c r="G36">
+        <v>0.116</v>
+      </c>
+      <c r="H36">
+        <v>10.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K36">
+        <v>0.004</v>
+      </c>
+      <c r="L36">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M36">
+        <v>4.059600000000001</v>
+      </c>
+      <c r="N36">
+        <v>-3.9926</v>
+      </c>
+      <c r="O36">
+        <v>-0.3992599999999999</v>
+      </c>
+      <c r="P36">
+        <v>-3.59334</v>
+      </c>
+      <c r="Q36">
+        <v>-3.58934</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.105375494702643</v>
+      </c>
+      <c r="T36">
+        <v>0.7676079713099834</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.001650408907281505</v>
+      </c>
+      <c r="W36">
+        <v>0.2384058823529412</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.01650408907281509</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1526058265037444</v>
+      </c>
+      <c r="C37">
+        <v>11.34898232149693</v>
+      </c>
+      <c r="D37">
+        <v>28.73298232149693</v>
+      </c>
+      <c r="E37">
+        <v>-22</v>
+      </c>
+      <c r="F37">
+        <v>17.5</v>
+      </c>
+      <c r="G37">
+        <v>0.116</v>
+      </c>
+      <c r="H37">
+        <v>10.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K37">
+        <v>0.004</v>
+      </c>
+      <c r="L37">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M37">
+        <v>4.179</v>
+      </c>
+      <c r="N37">
+        <v>-4.112</v>
+      </c>
+      <c r="O37">
+        <v>-0.4111999999999999</v>
+      </c>
+      <c r="P37">
+        <v>-3.7008</v>
+      </c>
+      <c r="Q37">
+        <v>-3.6968</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1063997330826836</v>
+      </c>
+      <c r="T37">
+        <v>0.7794173247147523</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.001603254367073462</v>
+      </c>
+      <c r="W37">
+        <v>0.2384171428571429</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.0160325436707347</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1546058265037443</v>
+      </c>
+      <c r="C38">
+        <v>10.35275543570087</v>
+      </c>
+      <c r="D38">
+        <v>28.23675543570087</v>
+      </c>
+      <c r="E38">
+        <v>-21.5</v>
+      </c>
+      <c r="F38">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>0.116</v>
+      </c>
+      <c r="H38">
+        <v>10.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K38">
+        <v>0.004</v>
+      </c>
+      <c r="L38">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M38">
+        <v>4.2984</v>
+      </c>
+      <c r="N38">
+        <v>-4.2314</v>
+      </c>
+      <c r="O38">
+        <v>-0.4231399999999999</v>
+      </c>
+      <c r="P38">
+        <v>-3.80826</v>
+      </c>
+      <c r="Q38">
+        <v>-3.80426</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1074559789121005</v>
+      </c>
+      <c r="T38">
+        <v>0.7915957204134202</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.001558719523543644</v>
+      </c>
+      <c r="W38">
+        <v>0.2384277777777778</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.0155871952354365</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1566058265037444</v>
+      </c>
+      <c r="C39">
+        <v>9.373377525902768</v>
+      </c>
+      <c r="D39">
+        <v>27.75737752590277</v>
+      </c>
+      <c r="E39">
+        <v>-21</v>
+      </c>
+      <c r="F39">
+        <v>18.5</v>
+      </c>
+      <c r="G39">
+        <v>0.116</v>
+      </c>
+      <c r="H39">
+        <v>10.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K39">
+        <v>0.004</v>
+      </c>
+      <c r="L39">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M39">
+        <v>4.417800000000001</v>
+      </c>
+      <c r="N39">
+        <v>-4.3508</v>
+      </c>
+      <c r="O39">
+        <v>-0.43508</v>
+      </c>
+      <c r="P39">
+        <v>-3.91572</v>
+      </c>
+      <c r="Q39">
+        <v>-3.91172</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1085457563551498</v>
+      </c>
+      <c r="T39">
+        <v>0.804160731848554</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.001516591968853275</v>
+      </c>
+      <c r="W39">
+        <v>0.2384378378378379</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.01516591968853276</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1586058265037443</v>
+      </c>
+      <c r="C40">
+        <v>8.410004777916509</v>
+      </c>
+      <c r="D40">
+        <v>27.29400477791651</v>
+      </c>
+      <c r="E40">
+        <v>-20.5</v>
+      </c>
+      <c r="F40">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>0.116</v>
+      </c>
+      <c r="H40">
+        <v>10.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K40">
+        <v>0.004</v>
+      </c>
+      <c r="L40">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M40">
+        <v>4.5372</v>
+      </c>
+      <c r="N40">
+        <v>-4.4702</v>
+      </c>
+      <c r="O40">
+        <v>-0.4470199999999999</v>
+      </c>
+      <c r="P40">
+        <v>-4.02318</v>
+      </c>
+      <c r="Q40">
+        <v>-4.01918</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1096706879092651</v>
+      </c>
+      <c r="T40">
+        <v>0.817131066233208</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.001476681653883452</v>
+      </c>
+      <c r="W40">
+        <v>0.2384473684210526</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.0147668165388346</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1606058265037444</v>
+      </c>
+      <c r="C41">
+        <v>7.461848797839842</v>
+      </c>
+      <c r="D41">
+        <v>26.84584879783984</v>
+      </c>
+      <c r="E41">
+        <v>-20</v>
+      </c>
+      <c r="F41">
+        <v>19.5</v>
+      </c>
+      <c r="G41">
+        <v>0.116</v>
+      </c>
+      <c r="H41">
+        <v>10.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K41">
+        <v>0.004</v>
+      </c>
+      <c r="L41">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M41">
+        <v>4.6566</v>
+      </c>
+      <c r="N41">
+        <v>-4.5896</v>
+      </c>
+      <c r="O41">
+        <v>-0.4589599999999999</v>
+      </c>
+      <c r="P41">
+        <v>-4.13064</v>
+      </c>
+      <c r="Q41">
+        <v>-4.12664</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1108325024651547</v>
+      </c>
+      <c r="T41">
+        <v>0.8305266574829326</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.001438818021732594</v>
+      </c>
+      <c r="W41">
+        <v>0.2384564102564103</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.01438818021732602</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1626058265037444</v>
+      </c>
+      <c r="C42">
+        <v>6.528172135667116</v>
+      </c>
+      <c r="D42">
+        <v>26.41217213566712</v>
+      </c>
+      <c r="E42">
+        <v>-19.5</v>
+      </c>
+      <c r="F42">
+        <v>20</v>
+      </c>
+      <c r="G42">
+        <v>0.116</v>
+      </c>
+      <c r="H42">
+        <v>10.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K42">
+        <v>0.004</v>
+      </c>
+      <c r="L42">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M42">
+        <v>4.776</v>
+      </c>
+      <c r="N42">
+        <v>-4.709</v>
+      </c>
+      <c r="O42">
+        <v>-0.4708999999999999</v>
+      </c>
+      <c r="P42">
+        <v>-4.238099999999999</v>
+      </c>
+      <c r="Q42">
+        <v>-4.2341</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1120330441729073</v>
+      </c>
+      <c r="T42">
+        <v>0.8443687684409816</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.001402847571189279</v>
+      </c>
+      <c r="W42">
+        <v>0.238465</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.01402847571189281</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1646058265037443</v>
+      </c>
+      <c r="C43">
+        <v>5.608284235882433</v>
+      </c>
+      <c r="D43">
+        <v>25.99228423588243</v>
+      </c>
+      <c r="E43">
+        <v>-19</v>
+      </c>
+      <c r="F43">
+        <v>20.5</v>
+      </c>
+      <c r="G43">
+        <v>0.116</v>
+      </c>
+      <c r="H43">
+        <v>10.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K43">
+        <v>0.004</v>
+      </c>
+      <c r="L43">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M43">
+        <v>4.8954</v>
+      </c>
+      <c r="N43">
+        <v>-4.8284</v>
+      </c>
+      <c r="O43">
+        <v>-0.4828399999999999</v>
+      </c>
+      <c r="P43">
+        <v>-4.345560000000001</v>
+      </c>
+      <c r="Q43">
+        <v>-4.341560000000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1132742822097362</v>
+      </c>
+      <c r="T43">
+        <v>0.8586801034993032</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.001368631776770028</v>
+      </c>
+      <c r="W43">
+        <v>0.2384731707317073</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.01368631776770035</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1666058265037443</v>
+      </c>
+      <c r="C44">
+        <v>4.701537768261556</v>
+      </c>
+      <c r="D44">
+        <v>25.58553776826156</v>
+      </c>
+      <c r="E44">
+        <v>-18.5</v>
+      </c>
+      <c r="F44">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0.116</v>
+      </c>
+      <c r="H44">
+        <v>10.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K44">
+        <v>0.004</v>
+      </c>
+      <c r="L44">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M44">
+        <v>5.0148</v>
+      </c>
+      <c r="N44">
+        <v>-4.9478</v>
+      </c>
+      <c r="O44">
+        <v>-0.4947799999999999</v>
+      </c>
+      <c r="P44">
+        <v>-4.45302</v>
+      </c>
+      <c r="Q44">
+        <v>-4.449020000000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1145583215581799</v>
+      </c>
+      <c r="T44">
+        <v>0.8734849328699809</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.001336045305894552</v>
+      </c>
+      <c r="W44">
+        <v>0.2384809523809524</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.01336045305894551</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1686058265037443</v>
+      </c>
+      <c r="C45">
+        <v>3.807325297875664</v>
+      </c>
+      <c r="D45">
+        <v>25.19132529787566</v>
+      </c>
+      <c r="E45">
+        <v>-18</v>
+      </c>
+      <c r="F45">
+        <v>21.5</v>
+      </c>
+      <c r="G45">
+        <v>0.116</v>
+      </c>
+      <c r="H45">
+        <v>10.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K45">
+        <v>0.004</v>
+      </c>
+      <c r="L45">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M45">
+        <v>5.1342</v>
+      </c>
+      <c r="N45">
+        <v>-5.0672</v>
+      </c>
+      <c r="O45">
+        <v>-0.5067199999999998</v>
+      </c>
+      <c r="P45">
+        <v>-4.56048</v>
+      </c>
+      <c r="Q45">
+        <v>-4.556480000000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1158874149188497</v>
+      </c>
+      <c r="T45">
+        <v>0.8888092299378753</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.001304974484827236</v>
+      </c>
+      <c r="W45">
+        <v>0.2384883720930233</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01304974484827237</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1706058265037443</v>
+      </c>
+      <c r="C46">
+        <v>2.925076258267993</v>
+      </c>
+      <c r="D46">
+        <v>24.80907625826799</v>
+      </c>
+      <c r="E46">
+        <v>-17.5</v>
+      </c>
+      <c r="F46">
+        <v>22</v>
+      </c>
+      <c r="G46">
+        <v>0.116</v>
+      </c>
+      <c r="H46">
+        <v>10.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K46">
+        <v>0.004</v>
+      </c>
+      <c r="L46">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M46">
+        <v>5.2536</v>
+      </c>
+      <c r="N46">
+        <v>-5.1866</v>
+      </c>
+      <c r="O46">
+        <v>-0.5186599999999999</v>
+      </c>
+      <c r="P46">
+        <v>-4.667940000000001</v>
+      </c>
+      <c r="Q46">
+        <v>-4.663940000000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1172639758995435</v>
+      </c>
+      <c r="T46">
+        <v>0.9046808233296231</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.001275315973808436</v>
+      </c>
+      <c r="W46">
+        <v>0.2384954545454545</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01275315973808444</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1726058265037443</v>
+      </c>
+      <c r="C47">
+        <v>2.054254196082624</v>
+      </c>
+      <c r="D47">
+        <v>24.43825419608262</v>
+      </c>
+      <c r="E47">
+        <v>-17</v>
+      </c>
+      <c r="F47">
+        <v>22.5</v>
+      </c>
+      <c r="G47">
+        <v>0.116</v>
+      </c>
+      <c r="H47">
+        <v>10.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K47">
+        <v>0.004</v>
+      </c>
+      <c r="L47">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M47">
+        <v>5.373</v>
+      </c>
+      <c r="N47">
+        <v>-5.306</v>
+      </c>
+      <c r="O47">
+        <v>-0.5305999999999998</v>
+      </c>
+      <c r="P47">
+        <v>-4.7754</v>
+      </c>
+      <c r="Q47">
+        <v>-4.771400000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1186905936431715</v>
+      </c>
+      <c r="T47">
+        <v>0.9211295655719798</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.001246975618834915</v>
+      </c>
+      <c r="W47">
+        <v>0.2385022222222222</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.01246975618834922</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1746058265037443</v>
+      </c>
+      <c r="C48">
+        <v>1.194354259161898</v>
+      </c>
+      <c r="D48">
+        <v>24.0783542591619</v>
+      </c>
+      <c r="E48">
+        <v>-16.5</v>
+      </c>
+      <c r="F48">
+        <v>23</v>
+      </c>
+      <c r="G48">
+        <v>0.116</v>
+      </c>
+      <c r="H48">
+        <v>10.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K48">
+        <v>0.004</v>
+      </c>
+      <c r="L48">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M48">
+        <v>5.4924</v>
+      </c>
+      <c r="N48">
+        <v>-5.4254</v>
+      </c>
+      <c r="O48">
+        <v>-0.5425399999999999</v>
+      </c>
+      <c r="P48">
+        <v>-4.88286</v>
+      </c>
+      <c r="Q48">
+        <v>-4.87886</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.120170049081008</v>
+      </c>
+      <c r="T48">
+        <v>0.9381875204899794</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.001219867453208069</v>
+      </c>
+      <c r="W48">
+        <v>0.2385086956521739</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.01219867453208068</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1766058265037444</v>
+      </c>
+      <c r="C49">
+        <v>0.3449009033778694</v>
+      </c>
+      <c r="D49">
+        <v>23.72890090337787</v>
+      </c>
+      <c r="E49">
+        <v>-16</v>
+      </c>
+      <c r="F49">
+        <v>23.5</v>
+      </c>
+      <c r="G49">
+        <v>0.116</v>
+      </c>
+      <c r="H49">
+        <v>10.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K49">
+        <v>0.004</v>
+      </c>
+      <c r="L49">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M49">
+        <v>5.611800000000001</v>
+      </c>
+      <c r="N49">
+        <v>-5.5448</v>
+      </c>
+      <c r="O49">
+        <v>-0.5544799999999999</v>
+      </c>
+      <c r="P49">
+        <v>-4.990320000000001</v>
+      </c>
+      <c r="Q49">
+        <v>-4.986320000000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1217053330259327</v>
+      </c>
+      <c r="T49">
+        <v>0.9558891718199791</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.001193912826544067</v>
+      </c>
+      <c r="W49">
+        <v>0.2385148936170213</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.01193912826544075</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1786058265037443</v>
+      </c>
+      <c r="C50">
+        <v>-0.4945542037058388</v>
+      </c>
+      <c r="D50">
+        <v>23.38944579629416</v>
+      </c>
+      <c r="E50">
+        <v>-15.5</v>
+      </c>
+      <c r="F50">
+        <v>24</v>
+      </c>
+      <c r="G50">
+        <v>0.116</v>
+      </c>
+      <c r="H50">
+        <v>10.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K50">
+        <v>0.004</v>
+      </c>
+      <c r="L50">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M50">
+        <v>5.7312</v>
+      </c>
+      <c r="N50">
+        <v>-5.6642</v>
+      </c>
+      <c r="O50">
+        <v>-0.5664199999999999</v>
+      </c>
+      <c r="P50">
+        <v>-5.09778</v>
+      </c>
+      <c r="Q50">
+        <v>-5.093780000000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1232996663533545</v>
+      </c>
+      <c r="T50">
+        <v>0.9742716558934402</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.001169039642657733</v>
+      </c>
+      <c r="W50">
+        <v>0.2385208333333333</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01169039642657732</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1806058265037443</v>
+      </c>
+      <c r="C51">
+        <v>-1.324434101774433</v>
+      </c>
+      <c r="D51">
+        <v>23.05956589822557</v>
+      </c>
+      <c r="E51">
+        <v>-15</v>
+      </c>
+      <c r="F51">
+        <v>24.5</v>
+      </c>
+      <c r="G51">
+        <v>0.116</v>
+      </c>
+      <c r="H51">
+        <v>10.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K51">
+        <v>0.004</v>
+      </c>
+      <c r="L51">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M51">
+        <v>5.8506</v>
+      </c>
+      <c r="N51">
+        <v>-5.7836</v>
+      </c>
+      <c r="O51">
+        <v>-0.5783599999999999</v>
+      </c>
+      <c r="P51">
+        <v>-5.20524</v>
+      </c>
+      <c r="Q51">
+        <v>-5.20124</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1249565225563615</v>
+      </c>
+      <c r="T51">
+        <v>0.9933750216952724</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.001145181690766759</v>
+      </c>
+      <c r="W51">
+        <v>0.2385265306122449</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.01145181690766761</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1826058265037444</v>
+      </c>
+      <c r="C52">
+        <v>-2.145138296574569</v>
+      </c>
+      <c r="D52">
+        <v>22.73886170342543</v>
+      </c>
+      <c r="E52">
+        <v>-14.5</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>0.116</v>
+      </c>
+      <c r="H52">
+        <v>10.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K52">
+        <v>0.004</v>
+      </c>
+      <c r="L52">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M52">
+        <v>5.970000000000001</v>
+      </c>
+      <c r="N52">
+        <v>-5.903</v>
+      </c>
+      <c r="O52">
+        <v>-0.5902999999999999</v>
+      </c>
+      <c r="P52">
+        <v>-5.3127</v>
+      </c>
+      <c r="Q52">
+        <v>-5.308700000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1266796530074887</v>
+      </c>
+      <c r="T52">
+        <v>1.013242522129178</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.001122278056951423</v>
+      </c>
+      <c r="W52">
+        <v>0.238532</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.01122278056951431</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1846058265037444</v>
+      </c>
+      <c r="C53">
+        <v>-2.95704437397459</v>
+      </c>
+      <c r="D53">
+        <v>22.42695562602541</v>
+      </c>
+      <c r="E53">
+        <v>-14</v>
+      </c>
+      <c r="F53">
+        <v>25.5</v>
+      </c>
+      <c r="G53">
+        <v>0.116</v>
+      </c>
+      <c r="H53">
+        <v>10.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K53">
+        <v>0.004</v>
+      </c>
+      <c r="L53">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M53">
+        <v>6.0894</v>
+      </c>
+      <c r="N53">
+        <v>-6.0224</v>
+      </c>
+      <c r="O53">
+        <v>-0.6022399999999999</v>
+      </c>
+      <c r="P53">
+        <v>-5.42016</v>
+      </c>
+      <c r="Q53">
+        <v>-5.416160000000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.128473115313764</v>
+      </c>
+      <c r="T53">
+        <v>1.03392094094814</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.001100272604854337</v>
+      </c>
+      <c r="W53">
+        <v>0.2385372549019608</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.01100272604854335</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1866058265037444</v>
+      </c>
+      <c r="C54">
+        <v>-3.760509482983096</v>
+      </c>
+      <c r="D54">
+        <v>22.1234905170169</v>
+      </c>
+      <c r="E54">
+        <v>-13.5</v>
+      </c>
+      <c r="F54">
+        <v>26</v>
+      </c>
+      <c r="G54">
+        <v>0.116</v>
+      </c>
+      <c r="H54">
+        <v>10.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K54">
+        <v>0.004</v>
+      </c>
+      <c r="L54">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M54">
+        <v>6.2088</v>
+      </c>
+      <c r="N54">
+        <v>-6.1418</v>
+      </c>
+      <c r="O54">
+        <v>-0.6141799999999998</v>
+      </c>
+      <c r="P54">
+        <v>-5.52762</v>
+      </c>
+      <c r="Q54">
+        <v>-5.52362</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1303413052161341</v>
+      </c>
+      <c r="T54">
+        <v>1.055460960551227</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.001079113516299446</v>
+      </c>
+      <c r="W54">
+        <v>0.2385423076923077</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.01079113516299446</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1886058265037444</v>
+      </c>
+      <c r="C55">
+        <v>-4.555871699972219</v>
+      </c>
+      <c r="D55">
+        <v>21.82812830002778</v>
+      </c>
+      <c r="E55">
+        <v>-13</v>
+      </c>
+      <c r="F55">
+        <v>26.5</v>
+      </c>
+      <c r="G55">
+        <v>0.116</v>
+      </c>
+      <c r="H55">
+        <v>10.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K55">
+        <v>0.004</v>
+      </c>
+      <c r="L55">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M55">
+        <v>6.328200000000001</v>
+      </c>
+      <c r="N55">
+        <v>-6.261200000000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.6261199999999999</v>
+      </c>
+      <c r="P55">
+        <v>-5.63508</v>
+      </c>
+      <c r="Q55">
+        <v>-5.631080000000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1322889925611582</v>
+      </c>
+      <c r="T55">
+        <v>1.077917576733168</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.001058752883916437</v>
+      </c>
+      <c r="W55">
+        <v>0.2385471698113208</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.01058752883916436</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1906058265037444</v>
+      </c>
+      <c r="C56">
+        <v>-5.34345128506132</v>
+      </c>
+      <c r="D56">
+        <v>21.54054871493868</v>
+      </c>
+      <c r="E56">
+        <v>-12.5</v>
+      </c>
+      <c r="F56">
+        <v>27</v>
+      </c>
+      <c r="G56">
+        <v>0.116</v>
+      </c>
+      <c r="H56">
+        <v>10.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K56">
+        <v>0.004</v>
+      </c>
+      <c r="L56">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M56">
+        <v>6.4476</v>
+      </c>
+      <c r="N56">
+        <v>-6.3806</v>
+      </c>
+      <c r="O56">
+        <v>-0.6380599999999998</v>
+      </c>
+      <c r="P56">
+        <v>-5.74254</v>
+      </c>
+      <c r="Q56">
+        <v>-5.73854</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1343213619646617</v>
+      </c>
+      <c r="T56">
+        <v>1.101350567531715</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.001039146349029096</v>
+      </c>
+      <c r="W56">
+        <v>0.2385518518518518</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.01039146349029096</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1926058265037444</v>
+      </c>
+      <c r="C57">
+        <v>-6.123551840477081</v>
+      </c>
+      <c r="D57">
+        <v>21.26044815952292</v>
+      </c>
+      <c r="E57">
+        <v>-12</v>
+      </c>
+      <c r="F57">
+        <v>27.5</v>
+      </c>
+      <c r="G57">
+        <v>0.116</v>
+      </c>
+      <c r="H57">
+        <v>10.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K57">
+        <v>0.004</v>
+      </c>
+      <c r="L57">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M57">
+        <v>6.567000000000001</v>
+      </c>
+      <c r="N57">
+        <v>-6.500000000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="P57">
+        <v>-5.850000000000001</v>
+      </c>
+      <c r="Q57">
+        <v>-5.846000000000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1364440588972097</v>
+      </c>
+      <c r="T57">
+        <v>1.125825024587976</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.001020252779046748</v>
+      </c>
+      <c r="W57">
+        <v>0.2385563636363636</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.01020252779046749</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1946058265037444</v>
+      </c>
+      <c r="C58">
+        <v>-6.896461379697836</v>
+      </c>
+      <c r="D58">
+        <v>20.98753862030217</v>
+      </c>
+      <c r="E58">
+        <v>-11.5</v>
+      </c>
+      <c r="F58">
+        <v>28</v>
+      </c>
+      <c r="G58">
+        <v>0.116</v>
+      </c>
+      <c r="H58">
+        <v>10.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K58">
+        <v>0.004</v>
+      </c>
+      <c r="L58">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M58">
+        <v>6.686400000000001</v>
+      </c>
+      <c r="N58">
+        <v>-6.619400000000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.6619399999999999</v>
+      </c>
+      <c r="P58">
+        <v>-5.957460000000001</v>
+      </c>
+      <c r="Q58">
+        <v>-5.953460000000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1386632420539645</v>
+      </c>
+      <c r="T58">
+        <v>1.151411956964975</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.001002033979420914</v>
+      </c>
+      <c r="W58">
+        <v>0.2385607142857143</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.01002033979420913</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1966058265037444</v>
+      </c>
+      <c r="C59">
+        <v>-7.662453315297299</v>
+      </c>
+      <c r="D59">
+        <v>20.72154668470271</v>
+      </c>
+      <c r="E59">
+        <v>-11</v>
+      </c>
+      <c r="F59">
+        <v>28.5</v>
+      </c>
+      <c r="G59">
+        <v>0.116</v>
+      </c>
+      <c r="H59">
+        <v>10.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K59">
+        <v>0.004</v>
+      </c>
+      <c r="L59">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M59">
+        <v>6.805800000000001</v>
+      </c>
+      <c r="N59">
+        <v>-6.738800000000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.6738799999999999</v>
+      </c>
+      <c r="P59">
+        <v>-6.064920000000002</v>
+      </c>
+      <c r="Q59">
+        <v>-6.060920000000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1409856430319636</v>
+      </c>
+      <c r="T59">
+        <v>1.178188979219974</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.0009844544359223011</v>
+      </c>
+      <c r="W59">
+        <v>0.2385649122807018</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.009844544359222995</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1986058265037443</v>
+      </c>
+      <c r="C60">
+        <v>-8.421787372609863</v>
+      </c>
+      <c r="D60">
+        <v>20.46221262739013</v>
+      </c>
+      <c r="E60">
+        <v>-10.5</v>
+      </c>
+      <c r="F60">
+        <v>29</v>
+      </c>
+      <c r="G60">
+        <v>0.116</v>
+      </c>
+      <c r="H60">
+        <v>10.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K60">
+        <v>0.004</v>
+      </c>
+      <c r="L60">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M60">
+        <v>6.925199999999999</v>
+      </c>
+      <c r="N60">
+        <v>-6.858199999999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.6858199999999998</v>
+      </c>
+      <c r="P60">
+        <v>-6.17238</v>
+      </c>
+      <c r="Q60">
+        <v>-6.16838</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1434186345327246</v>
+      </c>
+      <c r="T60">
+        <v>1.206241097772831</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.0009674810835788133</v>
+      </c>
+      <c r="W60">
+        <v>0.2385689655172414</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.009674810835788139</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2006058265037443</v>
+      </c>
+      <c r="C61">
+        <v>-9.174710435635863</v>
+      </c>
+      <c r="D61">
+        <v>20.20928956436414</v>
+      </c>
+      <c r="E61">
+        <v>-10</v>
+      </c>
+      <c r="F61">
+        <v>29.5</v>
+      </c>
+      <c r="G61">
+        <v>0.116</v>
+      </c>
+      <c r="H61">
+        <v>10.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K61">
+        <v>0.004</v>
+      </c>
+      <c r="L61">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M61">
+        <v>7.0446</v>
+      </c>
+      <c r="N61">
+        <v>-6.9776</v>
+      </c>
+      <c r="O61">
+        <v>-0.6977599999999998</v>
+      </c>
+      <c r="P61">
+        <v>-6.27984</v>
+      </c>
+      <c r="Q61">
+        <v>-6.275840000000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1459703085457179</v>
+      </c>
+      <c r="T61">
+        <v>1.235661612352656</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0009510830991113758</v>
+      </c>
+      <c r="W61">
+        <v>0.2385728813559322</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.009510830991113828</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2026058265037443</v>
+      </c>
+      <c r="C62">
+        <v>-9.921457330977859</v>
+      </c>
+      <c r="D62">
+        <v>19.96254266902214</v>
+      </c>
+      <c r="E62">
+        <v>-9.5</v>
+      </c>
+      <c r="F62">
+        <v>30</v>
+      </c>
+      <c r="G62">
+        <v>0.116</v>
+      </c>
+      <c r="H62">
+        <v>10.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K62">
+        <v>0.004</v>
+      </c>
+      <c r="L62">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M62">
+        <v>7.164000000000001</v>
+      </c>
+      <c r="N62">
+        <v>-7.097</v>
+      </c>
+      <c r="O62">
+        <v>-0.7096999999999999</v>
+      </c>
+      <c r="P62">
+        <v>-6.387300000000001</v>
+      </c>
+      <c r="Q62">
+        <v>-6.383300000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1486495662593609</v>
+      </c>
+      <c r="T62">
+        <v>1.266553152661472</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.000935231714126186</v>
+      </c>
+      <c r="W62">
+        <v>0.2385766666666667</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.009352317141261834</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2046058265037443</v>
+      </c>
+      <c r="C63">
+        <v>-10.66225155504057</v>
+      </c>
+      <c r="D63">
+        <v>19.72174844495943</v>
+      </c>
+      <c r="E63">
+        <v>-9</v>
+      </c>
+      <c r="F63">
+        <v>30.5</v>
+      </c>
+      <c r="G63">
+        <v>0.116</v>
+      </c>
+      <c r="H63">
+        <v>10.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K63">
+        <v>0.004</v>
+      </c>
+      <c r="L63">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M63">
+        <v>7.2834</v>
+      </c>
+      <c r="N63">
+        <v>-7.2164</v>
+      </c>
+      <c r="O63">
+        <v>-0.7216399999999998</v>
+      </c>
+      <c r="P63">
+        <v>-6.49476</v>
+      </c>
+      <c r="Q63">
+        <v>-6.490760000000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1514662218044727</v>
+      </c>
+      <c r="T63">
+        <v>1.299028874524587</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0009199000466814945</v>
+      </c>
+      <c r="W63">
+        <v>0.2385803278688525</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.009199000466814988</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2066058265037443</v>
+      </c>
+      <c r="C64">
+        <v>-11.39730594922776</v>
+      </c>
+      <c r="D64">
+        <v>19.48669405077224</v>
+      </c>
+      <c r="E64">
+        <v>-8.5</v>
+      </c>
+      <c r="F64">
+        <v>31</v>
+      </c>
+      <c r="G64">
+        <v>0.116</v>
+      </c>
+      <c r="H64">
+        <v>10.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K64">
+        <v>0.004</v>
+      </c>
+      <c r="L64">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M64">
+        <v>7.4028</v>
+      </c>
+      <c r="N64">
+        <v>-7.3358</v>
+      </c>
+      <c r="O64">
+        <v>-0.7335799999999998</v>
+      </c>
+      <c r="P64">
+        <v>-6.60222</v>
+      </c>
+      <c r="Q64">
+        <v>-6.59822</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1544311223782746</v>
+      </c>
+      <c r="T64">
+        <v>1.333213844906813</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0009050629491543737</v>
+      </c>
+      <c r="W64">
+        <v>0.2385838709677419</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.009050629491543782</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2086058265037443</v>
+      </c>
+      <c r="C65">
+        <v>-12.12682332742376</v>
+      </c>
+      <c r="D65">
+        <v>19.25717667257624</v>
+      </c>
+      <c r="E65">
+        <v>-8</v>
+      </c>
+      <c r="F65">
+        <v>31.5</v>
+      </c>
+      <c r="G65">
+        <v>0.116</v>
+      </c>
+      <c r="H65">
+        <v>10.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K65">
+        <v>0.004</v>
+      </c>
+      <c r="L65">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M65">
+        <v>7.522200000000001</v>
+      </c>
+      <c r="N65">
+        <v>-7.4552</v>
+      </c>
+      <c r="O65">
+        <v>-0.7455199999999998</v>
+      </c>
+      <c r="P65">
+        <v>-6.709680000000001</v>
+      </c>
+      <c r="Q65">
+        <v>-6.705680000000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1575562878479577</v>
+      </c>
+      <c r="T65">
+        <v>1.369246651525916</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0008906968705963677</v>
+      </c>
+      <c r="W65">
+        <v>0.2385873015873016</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.008906968705963747</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2106058265037443</v>
+      </c>
+      <c r="C66">
+        <v>-12.85099705964764</v>
+      </c>
+      <c r="D66">
+        <v>19.03300294035236</v>
+      </c>
+      <c r="E66">
+        <v>-7.5</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66">
+        <v>0.116</v>
+      </c>
+      <c r="H66">
+        <v>10.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K66">
+        <v>0.004</v>
+      </c>
+      <c r="L66">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M66">
+        <v>7.6416</v>
+      </c>
+      <c r="N66">
+        <v>-7.5746</v>
+      </c>
+      <c r="O66">
+        <v>-0.7574599999999998</v>
+      </c>
+      <c r="P66">
+        <v>-6.81714</v>
+      </c>
+      <c r="Q66">
+        <v>-6.813140000000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1608550736215121</v>
+      </c>
+      <c r="T66">
+        <v>1.407281280734969</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.0008767797319932994</v>
+      </c>
+      <c r="W66">
+        <v>0.238590625</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.008767797319933046</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2126058265037443</v>
+      </c>
+      <c r="C67">
+        <v>-13.57001161541044</v>
+      </c>
+      <c r="D67">
+        <v>18.81398838458956</v>
+      </c>
+      <c r="E67">
+        <v>-7</v>
+      </c>
+      <c r="F67">
+        <v>32.5</v>
+      </c>
+      <c r="G67">
+        <v>0.116</v>
+      </c>
+      <c r="H67">
+        <v>10.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K67">
+        <v>0.004</v>
+      </c>
+      <c r="L67">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M67">
+        <v>7.761</v>
+      </c>
+      <c r="N67">
+        <v>-7.694</v>
+      </c>
+      <c r="O67">
+        <v>-0.7693999999999999</v>
+      </c>
+      <c r="P67">
+        <v>-6.9246</v>
+      </c>
+      <c r="Q67">
+        <v>-6.9206</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1643423614392696</v>
+      </c>
+      <c r="T67">
+        <v>1.447489317327397</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0008632908130395564</v>
+      </c>
+      <c r="W67">
+        <v>0.2385938461538462</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.008632908130395633</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2146058265037444</v>
+      </c>
+      <c r="C68">
+        <v>-14.28404306998443</v>
+      </c>
+      <c r="D68">
+        <v>18.59995693001557</v>
+      </c>
+      <c r="E68">
+        <v>-6.5</v>
+      </c>
+      <c r="F68">
+        <v>33</v>
+      </c>
+      <c r="G68">
+        <v>0.116</v>
+      </c>
+      <c r="H68">
+        <v>10.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K68">
+        <v>0.004</v>
+      </c>
+      <c r="L68">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M68">
+        <v>7.880400000000001</v>
+      </c>
+      <c r="N68">
+        <v>-7.813400000000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.7813399999999999</v>
+      </c>
+      <c r="P68">
+        <v>-7.03206</v>
+      </c>
+      <c r="Q68">
+        <v>-7.028060000000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1680347838345422</v>
+      </c>
+      <c r="T68">
+        <v>1.490062532542909</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0008502106492056236</v>
+      </c>
+      <c r="W68">
+        <v>0.2385969696969697</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.008502106492056294</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2166058265037444</v>
+      </c>
+      <c r="C69">
+        <v>-14.99325957650453</v>
+      </c>
+      <c r="D69">
+        <v>18.39074042349547</v>
+      </c>
+      <c r="E69">
+        <v>-6</v>
+      </c>
+      <c r="F69">
+        <v>33.5</v>
+      </c>
+      <c r="G69">
+        <v>0.116</v>
+      </c>
+      <c r="H69">
+        <v>10.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K69">
+        <v>0.004</v>
+      </c>
+      <c r="L69">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M69">
+        <v>7.9998</v>
+      </c>
+      <c r="N69">
+        <v>-7.9328</v>
+      </c>
+      <c r="O69">
+        <v>-0.7932799999999999</v>
+      </c>
+      <c r="P69">
+        <v>-7.13952</v>
+      </c>
+      <c r="Q69">
+        <v>-7.135520000000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1719509894052859</v>
+      </c>
+      <c r="T69">
+        <v>1.535215942619967</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.0008375209380234502</v>
+      </c>
+      <c r="W69">
+        <v>0.2386</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.008375209380234505</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2186058265037444</v>
+      </c>
+      <c r="C70">
+        <v>-15.69782180656233</v>
+      </c>
+      <c r="D70">
+        <v>18.18617819343767</v>
+      </c>
+      <c r="E70">
+        <v>-5.5</v>
+      </c>
+      <c r="F70">
+        <v>34</v>
+      </c>
+      <c r="G70">
+        <v>0.116</v>
+      </c>
+      <c r="H70">
+        <v>10.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K70">
+        <v>0.004</v>
+      </c>
+      <c r="L70">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M70">
+        <v>8.119200000000001</v>
+      </c>
+      <c r="N70">
+        <v>-8.052200000000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.8052199999999999</v>
+      </c>
+      <c r="P70">
+        <v>-7.246980000000001</v>
+      </c>
+      <c r="Q70">
+        <v>-7.242980000000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1761119578242011</v>
+      </c>
+      <c r="T70">
+        <v>1.583191440826841</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0008252044536407524</v>
+      </c>
+      <c r="W70">
+        <v>0.2386029411764706</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.008252044536407599</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2206058265037444</v>
+      </c>
+      <c r="C71">
+        <v>-16.39788336171895</v>
+      </c>
+      <c r="D71">
+        <v>17.98611663828105</v>
+      </c>
+      <c r="E71">
+        <v>-5</v>
+      </c>
+      <c r="F71">
+        <v>34.5</v>
+      </c>
+      <c r="G71">
+        <v>0.116</v>
+      </c>
+      <c r="H71">
+        <v>10.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K71">
+        <v>0.004</v>
+      </c>
+      <c r="L71">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M71">
+        <v>8.2386</v>
+      </c>
+      <c r="N71">
+        <v>-8.1716</v>
+      </c>
+      <c r="O71">
+        <v>-0.8171599999999998</v>
+      </c>
+      <c r="P71">
+        <v>-7.35444</v>
+      </c>
+      <c r="Q71">
+        <v>-7.350440000000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1805413758185302</v>
+      </c>
+      <c r="T71">
+        <v>1.634262132466416</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0008132449688053793</v>
+      </c>
+      <c r="W71">
+        <v>0.2386057971014493</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.008132449688053822</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2226058265037444</v>
+      </c>
+      <c r="C72">
+        <v>-17.09359115815178</v>
+      </c>
+      <c r="D72">
+        <v>17.79040884184822</v>
+      </c>
+      <c r="E72">
+        <v>-4.5</v>
+      </c>
+      <c r="F72">
+        <v>35</v>
+      </c>
+      <c r="G72">
+        <v>0.116</v>
+      </c>
+      <c r="H72">
+        <v>10.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K72">
+        <v>0.004</v>
+      </c>
+      <c r="L72">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M72">
+        <v>8.358000000000001</v>
+      </c>
+      <c r="N72">
+        <v>-8.291</v>
+      </c>
+      <c r="O72">
+        <v>-0.8290999999999998</v>
+      </c>
+      <c r="P72">
+        <v>-7.461900000000001</v>
+      </c>
+      <c r="Q72">
+        <v>-7.457900000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1852660883458145</v>
+      </c>
+      <c r="T72">
+        <v>1.688737536881963</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0008016271835367308</v>
+      </c>
+      <c r="W72">
+        <v>0.2386085714285714</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.00801627183536735</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2246058265037444</v>
+      </c>
+      <c r="C73">
+        <v>-17.78508578645925</v>
+      </c>
+      <c r="D73">
+        <v>17.59891421354075</v>
+      </c>
+      <c r="E73">
+        <v>-4</v>
+      </c>
+      <c r="F73">
+        <v>35.5</v>
+      </c>
+      <c r="G73">
+        <v>0.116</v>
+      </c>
+      <c r="H73">
+        <v>10.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K73">
+        <v>0.004</v>
+      </c>
+      <c r="L73">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M73">
+        <v>8.477400000000001</v>
+      </c>
+      <c r="N73">
+        <v>-8.410400000000001</v>
+      </c>
+      <c r="O73">
+        <v>-0.8410399999999999</v>
+      </c>
+      <c r="P73">
+        <v>-7.569360000000001</v>
+      </c>
+      <c r="Q73">
+        <v>-7.565360000000002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1903166431163598</v>
+      </c>
+      <c r="T73">
+        <v>1.746969865739962</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0007903366598249459</v>
+      </c>
+      <c r="W73">
+        <v>0.2386112676056338</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.007903366598249528</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2266058265037444</v>
+      </c>
+      <c r="C74">
+        <v>-18.47250184847572</v>
+      </c>
+      <c r="D74">
+        <v>17.41149815152428</v>
+      </c>
+      <c r="E74">
+        <v>-3.5</v>
+      </c>
+      <c r="F74">
+        <v>36</v>
+      </c>
+      <c r="G74">
+        <v>0.116</v>
+      </c>
+      <c r="H74">
+        <v>10.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K74">
+        <v>0.004</v>
+      </c>
+      <c r="L74">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M74">
+        <v>8.5968</v>
+      </c>
+      <c r="N74">
+        <v>-8.5298</v>
+      </c>
+      <c r="O74">
+        <v>-0.8529799999999997</v>
+      </c>
+      <c r="P74">
+        <v>-7.67682</v>
+      </c>
+      <c r="Q74">
+        <v>-7.672820000000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1957279517990869</v>
+      </c>
+      <c r="T74">
+        <v>1.809361646659246</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0007793597617718218</v>
+      </c>
+      <c r="W74">
+        <v>0.2386138888888889</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.007793597617718251</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2286058265037444</v>
+      </c>
+      <c r="C75">
+        <v>-19.15596827279206</v>
+      </c>
+      <c r="D75">
+        <v>17.22803172720795</v>
+      </c>
+      <c r="E75">
+        <v>-3</v>
+      </c>
+      <c r="F75">
+        <v>36.5</v>
+      </c>
+      <c r="G75">
+        <v>0.116</v>
+      </c>
+      <c r="H75">
+        <v>10.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K75">
+        <v>0.004</v>
+      </c>
+      <c r="L75">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M75">
+        <v>8.716200000000001</v>
+      </c>
+      <c r="N75">
+        <v>-8.6492</v>
+      </c>
+      <c r="O75">
+        <v>-0.8649199999999998</v>
+      </c>
+      <c r="P75">
+        <v>-7.784280000000001</v>
+      </c>
+      <c r="Q75">
+        <v>-7.780280000000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2015400981620161</v>
+      </c>
+      <c r="T75">
+        <v>1.876375040979959</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0007686836006516597</v>
+      </c>
+      <c r="W75">
+        <v>0.2386164383561644</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.007686836006516651</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2306058265037443</v>
+      </c>
+      <c r="C76">
+        <v>-19.83560861053614</v>
+      </c>
+      <c r="D76">
+        <v>17.04839138946386</v>
+      </c>
+      <c r="E76">
+        <v>-2.5</v>
+      </c>
+      <c r="F76">
+        <v>37</v>
+      </c>
+      <c r="G76">
+        <v>0.116</v>
+      </c>
+      <c r="H76">
+        <v>10.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K76">
+        <v>0.004</v>
+      </c>
+      <c r="L76">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M76">
+        <v>8.835600000000001</v>
+      </c>
+      <c r="N76">
+        <v>-8.768600000000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.8768599999999999</v>
+      </c>
+      <c r="P76">
+        <v>-7.891740000000001</v>
+      </c>
+      <c r="Q76">
+        <v>-7.887740000000002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.207799332706709</v>
+      </c>
+      <c r="T76">
+        <v>1.94854331178688</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0007582959844266373</v>
+      </c>
+      <c r="W76">
+        <v>0.2386189189189189</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.007582959844266379</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2326058265037444</v>
+      </c>
+      <c r="C77">
+        <v>-20.51154131283944</v>
+      </c>
+      <c r="D77">
+        <v>16.87245868716056</v>
+      </c>
+      <c r="E77">
+        <v>-2</v>
+      </c>
+      <c r="F77">
+        <v>37.5</v>
+      </c>
+      <c r="G77">
+        <v>0.116</v>
+      </c>
+      <c r="H77">
+        <v>10.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K77">
+        <v>0.004</v>
+      </c>
+      <c r="L77">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M77">
+        <v>8.955</v>
+      </c>
+      <c r="N77">
+        <v>-8.888</v>
+      </c>
+      <c r="O77">
+        <v>-0.8887999999999998</v>
+      </c>
+      <c r="P77">
+        <v>-7.9992</v>
+      </c>
+      <c r="Q77">
+        <v>-7.995200000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2145593060149774</v>
+      </c>
+      <c r="T77">
+        <v>2.026485044258356</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0007481853713009489</v>
+      </c>
+      <c r="W77">
+        <v>0.2386213333333334</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.007481853713009468</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2346058265037444</v>
+      </c>
+      <c r="C78">
+        <v>-21.18387999129892</v>
+      </c>
+      <c r="D78">
+        <v>16.70012000870108</v>
+      </c>
+      <c r="E78">
+        <v>-1.5</v>
+      </c>
+      <c r="F78">
+        <v>38</v>
+      </c>
+      <c r="G78">
+        <v>0.116</v>
+      </c>
+      <c r="H78">
+        <v>10.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K78">
+        <v>0.004</v>
+      </c>
+      <c r="L78">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M78">
+        <v>9.074400000000001</v>
+      </c>
+      <c r="N78">
+        <v>-9.007400000000001</v>
+      </c>
+      <c r="O78">
+        <v>-0.9007399999999999</v>
+      </c>
+      <c r="P78">
+        <v>-8.106660000000002</v>
+      </c>
+      <c r="Q78">
+        <v>-8.102660000000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2218826104322681</v>
+      </c>
+      <c r="T78">
+        <v>2.110921921102454</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0007383408269417259</v>
+      </c>
+      <c r="W78">
+        <v>0.2386236842105263</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.007383408269417302</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2366058265037443</v>
+      </c>
+      <c r="C79">
+        <v>-21.85273366263792</v>
+      </c>
+      <c r="D79">
+        <v>16.53126633736208</v>
+      </c>
+      <c r="E79">
+        <v>-1</v>
+      </c>
+      <c r="F79">
+        <v>38.5</v>
+      </c>
+      <c r="G79">
+        <v>0.116</v>
+      </c>
+      <c r="H79">
+        <v>10.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K79">
+        <v>0.004</v>
+      </c>
+      <c r="L79">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M79">
+        <v>9.193800000000001</v>
+      </c>
+      <c r="N79">
+        <v>-9.126800000000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.9126799999999999</v>
+      </c>
+      <c r="P79">
+        <v>-8.214120000000001</v>
+      </c>
+      <c r="Q79">
+        <v>-8.210120000000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2298427239293233</v>
+      </c>
+      <c r="T79">
+        <v>2.20270113506343</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.0007287519850333917</v>
+      </c>
+      <c r="W79">
+        <v>0.238625974025974</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.007287519850333934</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2386058265037443</v>
+      </c>
+      <c r="C80">
+        <v>-22.51820697867309</v>
+      </c>
+      <c r="D80">
+        <v>16.36579302132691</v>
+      </c>
+      <c r="E80">
+        <v>-0.5</v>
+      </c>
+      <c r="F80">
+        <v>39</v>
+      </c>
+      <c r="G80">
+        <v>0.116</v>
+      </c>
+      <c r="H80">
+        <v>10.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K80">
+        <v>0.004</v>
+      </c>
+      <c r="L80">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M80">
+        <v>9.3132</v>
+      </c>
+      <c r="N80">
+        <v>-9.2462</v>
+      </c>
+      <c r="O80">
+        <v>-0.9246199999999998</v>
+      </c>
+      <c r="P80">
+        <v>-8.321580000000001</v>
+      </c>
+      <c r="Q80">
+        <v>-8.317580000000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2385264841079289</v>
+      </c>
+      <c r="T80">
+        <v>2.30282391392995</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0007194090108662971</v>
+      </c>
+      <c r="W80">
+        <v>0.2386282051282051</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.007194090108663009</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2406058265037444</v>
+      </c>
+      <c r="C81">
+        <v>-23.18040044260684</v>
+      </c>
+      <c r="D81">
+        <v>16.20359955739317</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>39.5</v>
+      </c>
+      <c r="G81">
+        <v>0.116</v>
+      </c>
+      <c r="H81">
+        <v>10.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K81">
+        <v>0.004</v>
+      </c>
+      <c r="L81">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M81">
+        <v>9.432600000000001</v>
+      </c>
+      <c r="N81">
+        <v>-9.365600000000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.9365599999999998</v>
+      </c>
+      <c r="P81">
+        <v>-8.429040000000001</v>
+      </c>
+      <c r="Q81">
+        <v>-8.425040000000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2480372690654493</v>
+      </c>
+      <c r="T81">
+        <v>2.412482195545662</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0007103025676907743</v>
+      </c>
+      <c r="W81">
+        <v>0.2386303797468355</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.007103025676907793</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2426058265037444</v>
+      </c>
+      <c r="C82">
+        <v>-23.83941061258444</v>
+      </c>
+      <c r="D82">
+        <v>16.04458938741556</v>
+      </c>
+      <c r="E82">
+        <v>0.5</v>
+      </c>
+      <c r="F82">
+        <v>40</v>
+      </c>
+      <c r="G82">
+        <v>0.116</v>
+      </c>
+      <c r="H82">
+        <v>10.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K82">
+        <v>0.004</v>
+      </c>
+      <c r="L82">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M82">
+        <v>9.552</v>
+      </c>
+      <c r="N82">
+        <v>-9.484999999999999</v>
+      </c>
+      <c r="O82">
+        <v>-0.9484999999999998</v>
+      </c>
+      <c r="P82">
+        <v>-8.5365</v>
+      </c>
+      <c r="Q82">
+        <v>-8.532500000000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2584991325187218</v>
+      </c>
+      <c r="T82">
+        <v>2.533106305322945</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0007014237855946396</v>
+      </c>
+      <c r="W82">
+        <v>0.2386325</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.007014237855946459</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2446058265037444</v>
+      </c>
+      <c r="C83">
+        <v>-24.49533029338243</v>
+      </c>
+      <c r="D83">
+        <v>15.88866970661757</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>40.5</v>
+      </c>
+      <c r="G83">
+        <v>0.116</v>
+      </c>
+      <c r="H83">
+        <v>10.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K83">
+        <v>0.004</v>
+      </c>
+      <c r="L83">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M83">
+        <v>9.6714</v>
+      </c>
+      <c r="N83">
+        <v>-9.6044</v>
+      </c>
+      <c r="O83">
+        <v>-0.9604399999999997</v>
+      </c>
+      <c r="P83">
+        <v>-8.64396</v>
+      </c>
+      <c r="Q83">
+        <v>-8.63996</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2700622447565493</v>
+      </c>
+      <c r="T83">
+        <v>2.666427689813627</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0006927642326860638</v>
+      </c>
+      <c r="W83">
+        <v>0.2386345679012346</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.006927642326860606</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2466058265037444</v>
+      </c>
+      <c r="C84">
+        <v>-25.1482487170276</v>
+      </c>
+      <c r="D84">
+        <v>15.7357512829724</v>
+      </c>
+      <c r="E84">
+        <v>1.5</v>
+      </c>
+      <c r="F84">
+        <v>41</v>
+      </c>
+      <c r="G84">
+        <v>0.116</v>
+      </c>
+      <c r="H84">
+        <v>10.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K84">
+        <v>0.004</v>
+      </c>
+      <c r="L84">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M84">
+        <v>9.790800000000001</v>
+      </c>
+      <c r="N84">
+        <v>-9.723800000000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.9723799999999998</v>
+      </c>
+      <c r="P84">
+        <v>-8.751420000000001</v>
+      </c>
+      <c r="Q84">
+        <v>-8.747420000000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2829101472430242</v>
+      </c>
+      <c r="T84">
+        <v>2.814562561469939</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0006843158883850142</v>
+      </c>
+      <c r="W84">
+        <v>0.2386365853658537</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.00684315888385012</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2486058265037444</v>
+      </c>
+      <c r="C85">
+        <v>-25.79825171308541</v>
+      </c>
+      <c r="D85">
+        <v>15.5857482869146</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85">
+        <v>41.5</v>
+      </c>
+      <c r="G85">
+        <v>0.116</v>
+      </c>
+      <c r="H85">
+        <v>10.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K85">
+        <v>0.004</v>
+      </c>
+      <c r="L85">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M85">
+        <v>9.9102</v>
+      </c>
+      <c r="N85">
+        <v>-9.8432</v>
+      </c>
+      <c r="O85">
+        <v>-0.9843199999999998</v>
+      </c>
+      <c r="P85">
+        <v>-8.858879999999999</v>
+      </c>
+      <c r="Q85">
+        <v>-8.85488</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2972695676690845</v>
+      </c>
+      <c r="T85">
+        <v>2.980125065085818</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0006760711186454358</v>
+      </c>
+      <c r="W85">
+        <v>0.2386385542168675</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.006760711186454382</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2506058265037444</v>
+      </c>
+      <c r="C86">
+        <v>-26.44542186930053</v>
+      </c>
+      <c r="D86">
+        <v>15.43857813069947</v>
+      </c>
+      <c r="E86">
+        <v>2.5</v>
+      </c>
+      <c r="F86">
+        <v>42</v>
+      </c>
+      <c r="G86">
+        <v>0.116</v>
+      </c>
+      <c r="H86">
+        <v>10.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K86">
+        <v>0.004</v>
+      </c>
+      <c r="L86">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M86">
+        <v>10.0296</v>
+      </c>
+      <c r="N86">
+        <v>-9.9626</v>
+      </c>
+      <c r="O86">
+        <v>-0.9962599999999998</v>
+      </c>
+      <c r="P86">
+        <v>-8.966340000000001</v>
+      </c>
+      <c r="Q86">
+        <v>-8.962340000000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3134239156484022</v>
+      </c>
+      <c r="T86">
+        <v>3.16638288165368</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0006680226529472758</v>
+      </c>
+      <c r="W86">
+        <v>0.2386404761904762</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.006680226529472755</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2526058265037444</v>
+      </c>
+      <c r="C87">
+        <v>-27.08983868322144</v>
+      </c>
+      <c r="D87">
+        <v>15.29416131677856</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87">
+        <v>42.5</v>
+      </c>
+      <c r="G87">
+        <v>0.116</v>
+      </c>
+      <c r="H87">
+        <v>10.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K87">
+        <v>0.004</v>
+      </c>
+      <c r="L87">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M87">
+        <v>10.149</v>
+      </c>
+      <c r="N87">
+        <v>-10.082</v>
+      </c>
+      <c r="O87">
+        <v>-1.0082</v>
+      </c>
+      <c r="P87">
+        <v>-9.0738</v>
+      </c>
+      <c r="Q87">
+        <v>-9.069800000000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.331732176691629</v>
+      </c>
+      <c r="T87">
+        <v>3.377475073763926</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0006601635629126019</v>
+      </c>
+      <c r="W87">
+        <v>0.2386423529411765</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.006601635629126079</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2546058265037444</v>
+      </c>
+      <c r="C88">
+        <v>-27.73157870539377</v>
+      </c>
+      <c r="D88">
+        <v>15.15242129460623</v>
+      </c>
+      <c r="E88">
+        <v>3.5</v>
+      </c>
+      <c r="F88">
+        <v>43</v>
+      </c>
+      <c r="G88">
+        <v>0.116</v>
+      </c>
+      <c r="H88">
+        <v>10.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K88">
+        <v>0.004</v>
+      </c>
+      <c r="L88">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M88">
+        <v>10.2684</v>
+      </c>
+      <c r="N88">
+        <v>-10.2014</v>
+      </c>
+      <c r="O88">
+        <v>-1.02014</v>
+      </c>
+      <c r="P88">
+        <v>-9.18126</v>
+      </c>
+      <c r="Q88">
+        <v>-9.17726</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3526559035981739</v>
+      </c>
+      <c r="T88">
+        <v>3.618723293318492</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0006524872424136182</v>
+      </c>
+      <c r="W88">
+        <v>0.2386441860465116</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.006524872424136241</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2566058265037444</v>
+      </c>
+      <c r="C89">
+        <v>-28.37071567466438</v>
+      </c>
+      <c r="D89">
+        <v>15.01328432533562</v>
+      </c>
+      <c r="E89">
+        <v>4</v>
+      </c>
+      <c r="F89">
+        <v>43.5</v>
+      </c>
+      <c r="G89">
+        <v>0.116</v>
+      </c>
+      <c r="H89">
+        <v>10.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K89">
+        <v>0.004</v>
+      </c>
+      <c r="L89">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M89">
+        <v>10.3878</v>
+      </c>
+      <c r="N89">
+        <v>-10.3208</v>
+      </c>
+      <c r="O89">
+        <v>-1.03208</v>
+      </c>
+      <c r="P89">
+        <v>-9.28872</v>
+      </c>
+      <c r="Q89">
+        <v>-9.28472</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3767986654134181</v>
+      </c>
+      <c r="T89">
+        <v>3.897086623573761</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0006449873890525421</v>
+      </c>
+      <c r="W89">
+        <v>0.2386459770114943</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.006449873890525426</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2586058265037444</v>
+      </c>
+      <c r="C90">
+        <v>-29.00732064609884</v>
+      </c>
+      <c r="D90">
+        <v>14.87667935390116</v>
+      </c>
+      <c r="E90">
+        <v>4.5</v>
+      </c>
+      <c r="F90">
+        <v>44</v>
+      </c>
+      <c r="G90">
+        <v>0.116</v>
+      </c>
+      <c r="H90">
+        <v>10.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K90">
+        <v>0.004</v>
+      </c>
+      <c r="L90">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M90">
+        <v>10.5072</v>
+      </c>
+      <c r="N90">
+        <v>-10.4402</v>
+      </c>
+      <c r="O90">
+        <v>-1.04402</v>
+      </c>
+      <c r="P90">
+        <v>-9.396180000000001</v>
+      </c>
+      <c r="Q90">
+        <v>-9.392180000000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4049652208645363</v>
+      </c>
+      <c r="T90">
+        <v>4.221843842204908</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0006376579869042178</v>
+      </c>
+      <c r="W90">
+        <v>0.2386477272727273</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.006376579869042165</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2606058265037444</v>
+      </c>
+      <c r="C91">
+        <v>-29.64146211197824</v>
+      </c>
+      <c r="D91">
+        <v>14.74253788802177</v>
+      </c>
+      <c r="E91">
+        <v>5</v>
+      </c>
+      <c r="F91">
+        <v>44.5</v>
+      </c>
+      <c r="G91">
+        <v>0.116</v>
+      </c>
+      <c r="H91">
+        <v>10.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K91">
+        <v>0.004</v>
+      </c>
+      <c r="L91">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M91">
+        <v>10.6266</v>
+      </c>
+      <c r="N91">
+        <v>-10.5596</v>
+      </c>
+      <c r="O91">
+        <v>-1.05596</v>
+      </c>
+      <c r="P91">
+        <v>-9.503640000000001</v>
+      </c>
+      <c r="Q91">
+        <v>-9.499640000000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4382529682158577</v>
+      </c>
+      <c r="T91">
+        <v>4.605647827859899</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0006304932904221479</v>
+      </c>
+      <c r="W91">
+        <v>0.2386494382022472</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.006304932904221516</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2626058265037444</v>
+      </c>
+      <c r="C92">
+        <v>-30.27320611630848</v>
+      </c>
+      <c r="D92">
+        <v>14.61079388369152</v>
+      </c>
+      <c r="E92">
+        <v>5.5</v>
+      </c>
+      <c r="F92">
+        <v>45</v>
+      </c>
+      <c r="G92">
+        <v>0.116</v>
+      </c>
+      <c r="H92">
+        <v>10.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K92">
+        <v>0.004</v>
+      </c>
+      <c r="L92">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M92">
+        <v>10.746</v>
+      </c>
+      <c r="N92">
+        <v>-10.679</v>
+      </c>
+      <c r="O92">
+        <v>-1.0679</v>
+      </c>
+      <c r="P92">
+        <v>-9.6111</v>
+      </c>
+      <c r="Q92">
+        <v>-9.607100000000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4781982650374436</v>
+      </c>
+      <c r="T92">
+        <v>5.06621261064589</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0006234878094174574</v>
+      </c>
+      <c r="W92">
+        <v>0.2386511111111111</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.006234878094174556</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2646058265037444</v>
+      </c>
+      <c r="C93">
+        <v>-30.90261636324424</v>
+      </c>
+      <c r="D93">
+        <v>14.48138363675576</v>
+      </c>
+      <c r="E93">
+        <v>6</v>
+      </c>
+      <c r="F93">
+        <v>45.5</v>
+      </c>
+      <c r="G93">
+        <v>0.116</v>
+      </c>
+      <c r="H93">
+        <v>10.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K93">
+        <v>0.004</v>
+      </c>
+      <c r="L93">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M93">
+        <v>10.8654</v>
+      </c>
+      <c r="N93">
+        <v>-10.7984</v>
+      </c>
+      <c r="O93">
+        <v>-1.07984</v>
+      </c>
+      <c r="P93">
+        <v>-9.71856</v>
+      </c>
+      <c r="Q93">
+        <v>-9.714560000000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5270202944860485</v>
+      </c>
+      <c r="T93">
+        <v>5.629125122939879</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0006166362950282546</v>
+      </c>
+      <c r="W93">
+        <v>0.2386527472527473</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.006166362950282611</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2666058265037444</v>
+      </c>
+      <c r="C94">
+        <v>-31.52975431980145</v>
+      </c>
+      <c r="D94">
+        <v>14.35424568019855</v>
+      </c>
+      <c r="E94">
+        <v>6.5</v>
+      </c>
+      <c r="F94">
+        <v>46</v>
+      </c>
+      <c r="G94">
+        <v>0.116</v>
+      </c>
+      <c r="H94">
+        <v>10.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K94">
+        <v>0.004</v>
+      </c>
+      <c r="L94">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M94">
+        <v>10.9848</v>
+      </c>
+      <c r="N94">
+        <v>-10.9178</v>
+      </c>
+      <c r="O94">
+        <v>-1.09178</v>
+      </c>
+      <c r="P94">
+        <v>-9.82602</v>
+      </c>
+      <c r="Q94">
+        <v>-9.82202</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5880478312968047</v>
+      </c>
+      <c r="T94">
+        <v>6.332765763307365</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0006099337266040344</v>
+      </c>
+      <c r="W94">
+        <v>0.238654347826087</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.006099337266040394</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2686058265037444</v>
+      </c>
+      <c r="C95">
+        <v>-32.15467931320639</v>
+      </c>
+      <c r="D95">
+        <v>14.22932068679361</v>
+      </c>
+      <c r="E95">
+        <v>7</v>
+      </c>
+      <c r="F95">
+        <v>46.5</v>
+      </c>
+      <c r="G95">
+        <v>0.116</v>
+      </c>
+      <c r="H95">
+        <v>10.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K95">
+        <v>0.004</v>
+      </c>
+      <c r="L95">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M95">
+        <v>11.1042</v>
+      </c>
+      <c r="N95">
+        <v>-11.0372</v>
+      </c>
+      <c r="O95">
+        <v>-1.10372</v>
+      </c>
+      <c r="P95">
+        <v>-9.933480000000001</v>
+      </c>
+      <c r="Q95">
+        <v>-9.929480000000002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6665118071963483</v>
+      </c>
+      <c r="T95">
+        <v>7.23744658663699</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0006033752994362491</v>
+      </c>
+      <c r="W95">
+        <v>0.2386559139784946</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.006033752994362485</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2706058265037444</v>
+      </c>
+      <c r="C96">
+        <v>-32.77744862320527</v>
+      </c>
+      <c r="D96">
+        <v>14.10655137679472</v>
+      </c>
+      <c r="E96">
+        <v>7.5</v>
+      </c>
+      <c r="F96">
+        <v>47</v>
+      </c>
+      <c r="G96">
+        <v>0.116</v>
+      </c>
+      <c r="H96">
+        <v>10.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K96">
+        <v>0.004</v>
+      </c>
+      <c r="L96">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M96">
+        <v>11.2236</v>
+      </c>
+      <c r="N96">
+        <v>-11.1566</v>
+      </c>
+      <c r="O96">
+        <v>-1.11566</v>
+      </c>
+      <c r="P96">
+        <v>-10.04094</v>
+      </c>
+      <c r="Q96">
+        <v>-10.03694</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7711304417290732</v>
+      </c>
+      <c r="T96">
+        <v>8.443687684409824</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0005969564132720336</v>
+      </c>
+      <c r="W96">
+        <v>0.2386574468085106</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.005969564132720317</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2726058265037444</v>
+      </c>
+      <c r="C97">
+        <v>-33.39811756963607</v>
+      </c>
+      <c r="D97">
+        <v>13.98588243036393</v>
+      </c>
+      <c r="E97">
+        <v>8</v>
+      </c>
+      <c r="F97">
+        <v>47.5</v>
+      </c>
+      <c r="G97">
+        <v>0.116</v>
+      </c>
+      <c r="H97">
+        <v>10.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K97">
+        <v>0.004</v>
+      </c>
+      <c r="L97">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M97">
+        <v>11.343</v>
+      </c>
+      <c r="N97">
+        <v>-11.276</v>
+      </c>
+      <c r="O97">
+        <v>-1.1276</v>
+      </c>
+      <c r="P97">
+        <v>-10.1484</v>
+      </c>
+      <c r="Q97">
+        <v>-10.1444</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9175965300748883</v>
+      </c>
+      <c r="T97">
+        <v>10.13242522129179</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0005906726615533806</v>
+      </c>
+      <c r="W97">
+        <v>0.2386589473684211</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.005906726615533819</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2746058265037444</v>
+      </c>
+      <c r="C98">
+        <v>-34.01673959554384</v>
+      </c>
+      <c r="D98">
+        <v>13.86726040445616</v>
+      </c>
+      <c r="E98">
+        <v>8.5</v>
+      </c>
+      <c r="F98">
+        <v>48</v>
+      </c>
+      <c r="G98">
+        <v>0.116</v>
+      </c>
+      <c r="H98">
+        <v>10.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K98">
+        <v>0.004</v>
+      </c>
+      <c r="L98">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M98">
+        <v>11.4624</v>
+      </c>
+      <c r="N98">
+        <v>-11.3954</v>
+      </c>
+      <c r="O98">
+        <v>-1.13954</v>
+      </c>
+      <c r="P98">
+        <v>-10.25586</v>
+      </c>
+      <c r="Q98">
+        <v>-10.25186</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.137295662593608</v>
+      </c>
+      <c r="T98">
+        <v>12.66553152661471</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0005845198213288664</v>
+      </c>
+      <c r="W98">
+        <v>0.2386604166666667</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.00584519821328866</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2766058265037444</v>
+      </c>
+      <c r="C99">
+        <v>-34.63336634610192</v>
+      </c>
+      <c r="D99">
+        <v>13.75063365389808</v>
+      </c>
+      <c r="E99">
+        <v>9</v>
+      </c>
+      <c r="F99">
+        <v>48.5</v>
+      </c>
+      <c r="G99">
+        <v>0.116</v>
+      </c>
+      <c r="H99">
+        <v>10.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K99">
+        <v>0.004</v>
+      </c>
+      <c r="L99">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M99">
+        <v>11.5818</v>
+      </c>
+      <c r="N99">
+        <v>-11.5148</v>
+      </c>
+      <c r="O99">
+        <v>-1.15148</v>
+      </c>
+      <c r="P99">
+        <v>-10.36332</v>
+      </c>
+      <c r="Q99">
+        <v>-10.35932</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.503460883458144</v>
+      </c>
+      <c r="T99">
+        <v>16.88737536881962</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0005784938437893934</v>
+      </c>
+      <c r="W99">
+        <v>0.2386618556701031</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.005784938437893961</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2786058265037443</v>
+      </c>
+      <c r="C100">
+        <v>-35.24804774358401</v>
+      </c>
+      <c r="D100">
+        <v>13.63595225641599</v>
+      </c>
+      <c r="E100">
+        <v>9.5</v>
+      </c>
+      <c r="F100">
+        <v>49</v>
+      </c>
+      <c r="G100">
+        <v>0.116</v>
+      </c>
+      <c r="H100">
+        <v>10.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K100">
+        <v>0.004</v>
+      </c>
+      <c r="L100">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M100">
+        <v>11.7012</v>
+      </c>
+      <c r="N100">
+        <v>-11.6342</v>
+      </c>
+      <c r="O100">
+        <v>-1.16342</v>
+      </c>
+      <c r="P100">
+        <v>-10.47078</v>
+      </c>
+      <c r="Q100">
+        <v>-10.46678</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.235791325187216</v>
+      </c>
+      <c r="T100">
+        <v>25.33106305322942</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0005725908453833793</v>
+      </c>
+      <c r="W100">
+        <v>0.2386632653061224</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.005725908453833806</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2806058265037443</v>
+      </c>
+      <c r="C101">
+        <v>-35.86083205861543</v>
+      </c>
+      <c r="D101">
+        <v>13.52316794138457</v>
+      </c>
+      <c r="E101">
+        <v>10</v>
+      </c>
+      <c r="F101">
+        <v>49.5</v>
+      </c>
+      <c r="G101">
+        <v>0.116</v>
+      </c>
+      <c r="H101">
+        <v>10.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K101">
+        <v>0.004</v>
+      </c>
+      <c r="L101">
+        <v>0.06699999999999999</v>
+      </c>
+      <c r="M101">
+        <v>11.8206</v>
+      </c>
+      <c r="N101">
+        <v>-11.7536</v>
+      </c>
+      <c r="O101">
+        <v>-1.17536</v>
+      </c>
+      <c r="P101">
+        <v>-10.57824</v>
+      </c>
+      <c r="Q101">
+        <v>-10.57424</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.432782650374431</v>
+      </c>
+      <c r="T101">
+        <v>50.66212610645885</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0005668070994704157</v>
+      </c>
+      <c r="W101">
+        <v>0.2386646464646465</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.005668070994704122</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
